--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\qiji\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67ADC50-EB9B-4740-9282-6DF1E514B73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E54F66F-F4E3-4CF7-A2EB-313A9D363160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill!$A$1:$Z$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill!$A$4:$Z$240</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="481">
   <si>
     <t>技能id</t>
   </si>
@@ -134,7 +134,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：主动技能；</t>
@@ -152,7 +151,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：被动技能；</t>
@@ -170,7 +168,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（不填默认为主动技能）</t>
@@ -189,7 +186,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：普通技能</t>
@@ -207,7 +203,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：天赋技能</t>
@@ -225,7 +220,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：连击技能</t>
@@ -243,7 +237,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：召唤技能</t>
@@ -261,7 +254,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：普通攻击技能</t>
@@ -279,7 +271,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：大天使天赋技能</t>
@@ -298,7 +289,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不显示</t>
@@ -316,7 +306,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>显示</t>
@@ -334,7 +323,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>激活时显示</t>
@@ -352,7 +340,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -370,7 +357,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不显示</t>
@@ -387,7 +373,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>显示</t>
@@ -412,7 +397,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>用于在界面中的排序</t>
@@ -430,7 +414,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>序号小的在前面</t>
@@ -449,7 +432,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>攻击（参考属性</t>
@@ -466,7 +448,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -483,7 +464,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -501,7 +481,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>魔攻（参考属性</t>
@@ -518,7 +497,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -535,7 +513,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -553,7 +530,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>无效果</t>
@@ -571,7 +547,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -589,7 +564,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>攻击力</t>
@@ -606,7 +580,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>魔法</t>
@@ -629,7 +602,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是否是范围技能</t>
@@ -647,7 +619,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -665,7 +636,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>否</t>
@@ -682,7 +652,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是</t>
@@ -709,7 +678,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：敌人</t>
@@ -727,7 +695,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：自己</t>
@@ -745,7 +712,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：玩家</t>
@@ -763,7 +729,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：红名</t>
@@ -781,7 +746,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：归属者</t>
@@ -799,7 +763,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>：队友和自己</t>
@@ -817,7 +780,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -835,7 +797,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -852,7 +813,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>友方</t>
@@ -869,7 +829,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不包含自己</t>
@@ -886,7 +845,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>友方</t>
@@ -903,7 +861,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>包含自己</t>
@@ -920,7 +877,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>自己</t>
@@ -959,7 +915,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>点</t>
@@ -976,7 +931,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>直线</t>
@@ -993,7 +947,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>扇形</t>
@@ -1010,7 +963,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>圆形</t>
@@ -1028,7 +980,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>大小受控与</t>
@@ -1045,7 +996,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>表的</t>
@@ -1062,7 +1012,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>列</t>
@@ -1080,7 +1029,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -1098,7 +1046,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>点</t>
@@ -1115,7 +1062,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>直线</t>
@@ -1132,7 +1078,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>扇形</t>
@@ -1149,7 +1094,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>圆形</t>
@@ -1176,7 +1120,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>点</t>
@@ -1193,7 +1136,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>十字</t>
@@ -1210,7 +1152,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>直线</t>
@@ -1227,7 +1168,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>横线</t>
@@ -1244,7 +1184,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>扇形</t>
@@ -1261,7 +1200,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>菱形</t>
@@ -1278,7 +1216,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>圆形</t>
@@ -1296,7 +1233,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>形状大小控制：</t>
@@ -1314,7 +1250,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -1332,7 +1267,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>点</t>
@@ -1349,7 +1283,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>十字</t>
@@ -1366,7 +1299,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>直线</t>
@@ -1383,7 +1315,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>横线</t>
@@ -1400,7 +1331,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>扇形</t>
@@ -1417,7 +1347,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>菱形</t>
@@ -1434,7 +1363,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>圆形</t>
@@ -1450,6 +1378,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>当</t>
     </r>
     <r>
@@ -1464,7 +1397,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>时进行判断</t>
@@ -1482,7 +1414,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>客户端发来的点（即目标位置）</t>
@@ -1500,7 +1431,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>自身所在点</t>
@@ -1519,7 +1449,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>或空</t>
@@ -1536,7 +1465,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>内挂不予显示</t>
@@ -1554,7 +1482,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体环境</t>
@@ -1572,7 +1499,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>群体环境</t>
@@ -1590,7 +1516,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>通用</t>
@@ -1607,7 +1532,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>状态</t>
@@ -1624,7 +1548,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>召唤</t>
@@ -1641,7 +1564,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>治疗</t>
@@ -1658,7 +1580,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>移动</t>
@@ -1675,7 +1596,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>三目标技能</t>
@@ -1693,7 +1613,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>公共环境</t>
@@ -1710,7 +1629,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（既可以适配单体环境又可以适配群体环境）</t>
@@ -1728,7 +1646,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>编辑器读取</t>
@@ -1746,7 +1663,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体</t>
@@ -1763,7 +1679,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>群体</t>
@@ -1780,7 +1695,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>状态</t>
@@ -1797,7 +1711,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>召唤</t>
@@ -1825,7 +1738,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>释放该技能时可获得的连击值</t>
@@ -1843,7 +1755,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单位：万分比</t>
@@ -1861,7 +1772,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不填表示该技能释放时不会获得连击值</t>
@@ -1880,7 +1790,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>或空，默认学习技能后，便会出现在挂机设置里</t>
@@ -1898,7 +1807,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>，学习技能后，不出现在挂机设置里</t>
@@ -1917,7 +1825,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>进入技能盘</t>
@@ -1935,7 +1842,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>不进入技能轮盘</t>
@@ -1953,7 +1859,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（不进入技能轮盘时，技能会在学习后直接进入特殊按钮中）</t>
@@ -1974,7 +1879,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>起手技</t>
@@ -1994,7 +1898,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>衔接技</t>
@@ -2014,7 +1917,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>终结技</t>
@@ -2034,7 +1936,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格式：如有多个类型可以用</t>
@@ -2053,7 +1954,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>分割</t>
@@ -2072,7 +1972,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>例如</t>
@@ -2092,7 +1991,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1、仅特殊技能需要配置
@@ -2111,7 +2009,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>时该字段不生效被过滤</t>
@@ -2671,7 +2568,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>恶灵</t>
@@ -2688,7 +2584,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>恶灵王毁灭烈焰</t>
@@ -2708,7 +2603,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>蓝</t>
@@ -2725,7 +2619,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>红魔龙喷射</t>
@@ -2739,7 +2632,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>蓝</t>
@@ -2756,7 +2648,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>红魔龙毁灭烈焰</t>
@@ -2851,7 +2742,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>鬼魅</t>
@@ -2868,7 +2758,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>剧毒鬼魅普攻</t>
@@ -2978,7 +2867,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>咒怨魔王</t>
@@ -2995,7 +2883,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格群体普攻</t>
@@ -3009,7 +2896,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>咒怨魔王</t>
@@ -3026,7 +2912,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格群体普攻</t>
@@ -3040,7 +2925,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>玛雅之手</t>
@@ -3057,7 +2941,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格群体普攻</t>
@@ -3071,7 +2954,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>玛雅之手</t>
@@ -3088,7 +2970,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>格群体普攻</t>
@@ -3209,9 +3090,6 @@
     <t>狂爆术</t>
   </si>
   <si>
-    <t>1014025</t>
-  </si>
-  <si>
     <t>防御值恢复</t>
   </si>
   <si>
@@ -3267,7 +3145,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>暴风雪术</t>
@@ -3284,7 +3161,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>大师技</t>
@@ -3395,6 +3271,12 @@
     <t>无影箭</t>
   </si>
   <si>
+    <t>星云召唤</t>
+  </si>
+  <si>
+    <t>惩戒屏障</t>
+  </si>
+  <si>
     <t>700</t>
   </si>
   <si>
@@ -3456,7 +3338,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>召唤兽</t>
@@ -3473,7 +3354,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>级普攻</t>
@@ -3487,7 +3367,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>召唤兽</t>
@@ -3504,7 +3383,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>级普攻</t>
@@ -3587,6 +3465,9 @@
   </si>
   <si>
     <t>1014018</t>
+  </si>
+  <si>
+    <t>1014025</t>
   </si>
   <si>
     <t>1014027</t>
@@ -3701,7 +3582,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3710,7 +3591,6 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3729,28 +3609,24 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3765,7 +3641,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3778,7 +3653,11 @@
       <u/>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3830,7 +3709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3895,6 +3774,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3952,11 +3834,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4510,25 +4415,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="52"/>
-      <tableStyleElement type="headerRow" dxfId="51"/>
-      <tableStyleElement type="totalRow" dxfId="50"/>
-      <tableStyleElement type="firstColumn" dxfId="49"/>
-      <tableStyleElement type="lastColumn" dxfId="48"/>
-      <tableStyleElement type="firstRowStripe" dxfId="47"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="46"/>
+      <tableStyleElement type="wholeTable" dxfId="54"/>
+      <tableStyleElement type="headerRow" dxfId="53"/>
+      <tableStyleElement type="totalRow" dxfId="52"/>
+      <tableStyleElement type="firstColumn" dxfId="51"/>
+      <tableStyleElement type="lastColumn" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="48"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="totalRow" dxfId="44"/>
-      <tableStyleElement type="firstRowStripe" dxfId="43"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="42"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="41"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="40"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="39"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="38"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="37"/>
-      <tableStyleElement type="pageFieldValues" dxfId="36"/>
+      <tableStyleElement type="headerRow" dxfId="47"/>
+      <tableStyleElement type="totalRow" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="44"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="43"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="42"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="41"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="40"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="39"/>
+      <tableStyleElement type="pageFieldValues" dxfId="38"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4801,7 +4706,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z238"/>
+  <dimension ref="A1:Z240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" customWidth="1"/>
@@ -4832,7 +4737,7 @@
     <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" ht="15" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4845,7 +4750,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
@@ -4912,7 +4817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="182.1" customHeight="1">
+    <row r="2" spans="1:26" ht="81" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -4992,7 +4897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -5072,7 +4977,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" ht="15.95" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>62</v>
       </c>
@@ -5166,10 +5071,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" s="26">
+        <v>0</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>89</v>
@@ -5210,8 +5115,11 @@
       <c r="S5" s="9">
         <v>1</v>
       </c>
+      <c r="U5" s="9">
+        <v>1</v>
+      </c>
       <c r="V5" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="16"/>
       <c r="Y5" s="1"/>
@@ -5231,10 +5139,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
@@ -5273,10 +5181,10 @@
         <v>1</v>
       </c>
       <c r="U6" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="16"/>
       <c r="Y6" s="1"/>
@@ -5296,7 +5204,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
       </c>
       <c r="H7" s="9">
         <v>1</v>
@@ -5332,6 +5243,12 @@
         <v>1</v>
       </c>
       <c r="S7" s="9">
+        <v>1</v>
+      </c>
+      <c r="U7" s="9">
+        <v>1</v>
+      </c>
+      <c r="V7" s="9">
         <v>1</v>
       </c>
       <c r="W7" s="16"/>
@@ -5342,16 +5259,19 @@
       <c r="A8" s="2">
         <v>1020063</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>0</v>
       </c>
       <c r="G8" s="2">
@@ -5391,6 +5311,12 @@
         <v>1</v>
       </c>
       <c r="S8" s="9">
+        <v>1</v>
+      </c>
+      <c r="U8" s="9">
+        <v>1</v>
+      </c>
+      <c r="V8" s="9">
         <v>1</v>
       </c>
       <c r="Y8" s="1"/>
@@ -6271,7 +6197,7 @@
       <c r="A22" s="9">
         <v>1200017</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="28" t="s">
         <v>109</v>
       </c>
       <c r="E22" s="9">
@@ -6327,7 +6253,7 @@
       <c r="A23" s="9">
         <v>1200018</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="28" t="s">
         <v>111</v>
       </c>
       <c r="E23" s="9">
@@ -6514,7 +6440,7 @@
       <c r="A26" s="9">
         <v>1303001</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="28" t="s">
         <v>114</v>
       </c>
       <c r="C26" s="9">
@@ -6576,7 +6502,7 @@
       <c r="A27" s="9">
         <v>1303002</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="28" t="s">
         <v>116</v>
       </c>
       <c r="C27" s="9">
@@ -6638,7 +6564,7 @@
       <c r="A28" s="9">
         <v>1303003</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="28" t="s">
         <v>117</v>
       </c>
       <c r="C28" s="9">
@@ -6700,7 +6626,7 @@
       <c r="A29" s="9">
         <v>1303004</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C29" s="9">
@@ -6755,14 +6681,14 @@
         <v>0</v>
       </c>
       <c r="W29" s="16"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" s="9" customFormat="1">
       <c r="A30" s="9">
         <v>1303005</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="28" t="s">
         <v>119</v>
       </c>
       <c r="C30" s="9">
@@ -6817,14 +6743,14 @@
         <v>0</v>
       </c>
       <c r="W30" s="16"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" s="9" customFormat="1">
       <c r="A31" s="9">
         <v>1303006</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="28" t="s">
         <v>120</v>
       </c>
       <c r="C31" s="9">
@@ -6879,14 +6805,14 @@
         <v>0</v>
       </c>
       <c r="W31" s="16"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
     </row>
     <row r="32" spans="1:26" s="9" customFormat="1">
       <c r="A32" s="9">
         <v>1303007</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="28" t="s">
         <v>121</v>
       </c>
       <c r="C32" s="9">
@@ -6948,7 +6874,7 @@
       <c r="A33" s="2">
         <v>1030001</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="30" t="s">
         <v>122</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -6998,7 +6924,7 @@
       <c r="A34" s="2">
         <v>1030002</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="30" t="s">
         <v>123</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -7053,7 +6979,7 @@
       <c r="A35" s="2">
         <v>1030003</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="30" t="s">
         <v>124</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -7930,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="9">
         <v>1</v>
@@ -8060,7 +7986,7 @@
       <c r="A50" s="9">
         <v>1300005</v>
       </c>
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="31" t="s">
         <v>141</v>
       </c>
       <c r="C50" s="9">
@@ -8085,7 +8011,7 @@
         <v>9500</v>
       </c>
       <c r="J50" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="9">
         <v>8</v>
@@ -8093,7 +8019,7 @@
       <c r="L50" s="9">
         <v>350</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>2</v>
       </c>
       <c r="N50" s="9">
@@ -8107,6 +8033,9 @@
       </c>
       <c r="Q50" s="9" t="s">
         <v>142</v>
+      </c>
+      <c r="R50" s="9">
+        <v>1</v>
       </c>
       <c r="S50" s="9">
         <v>0</v>
@@ -8119,7 +8048,7 @@
       <c r="A51" s="9">
         <v>1300003</v>
       </c>
-      <c r="B51" s="30" t="s">
+      <c r="B51" s="31" t="s">
         <v>143</v>
       </c>
       <c r="C51" s="9">
@@ -8181,7 +8110,7 @@
       <c r="A52" s="9">
         <v>1300004</v>
       </c>
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C52" s="9">
@@ -8243,7 +8172,7 @@
       <c r="A53" s="9">
         <v>1200011</v>
       </c>
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="31" t="s">
         <v>146</v>
       </c>
       <c r="C53" s="9">
@@ -8305,7 +8234,7 @@
       <c r="A54" s="9">
         <v>1100007</v>
       </c>
-      <c r="B54" s="30" t="s">
+      <c r="B54" s="31" t="s">
         <v>147</v>
       </c>
       <c r="C54" s="9">
@@ -8358,9 +8287,6 @@
       </c>
       <c r="S54" s="9">
         <v>0</v>
-      </c>
-      <c r="U54" s="9">
-        <v>1</v>
       </c>
       <c r="W54" s="16"/>
       <c r="Y54"/>
@@ -8370,7 +8296,7 @@
       <c r="A55" s="9">
         <v>1004019</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="27" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="9">
@@ -8380,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="9">
         <v>1</v>
@@ -8436,7 +8362,7 @@
       <c r="A56" s="9">
         <v>1004020</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="B56" s="27" t="s">
         <v>149</v>
       </c>
       <c r="C56" s="9">
@@ -8473,10 +8399,10 @@
         <v>1</v>
       </c>
       <c r="N56" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O56" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P56" s="2">
         <v>0</v>
@@ -8502,7 +8428,7 @@
       <c r="A57" s="9">
         <v>1004021</v>
       </c>
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="27" t="s">
         <v>150</v>
       </c>
       <c r="C57" s="9">
@@ -8568,7 +8494,7 @@
       <c r="A58" s="9">
         <v>1004022</v>
       </c>
-      <c r="B58" s="26" t="s">
+      <c r="B58" s="27" t="s">
         <v>151</v>
       </c>
       <c r="C58" s="9">
@@ -8634,7 +8560,7 @@
       <c r="A59" s="9">
         <v>1004023</v>
       </c>
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="33" t="s">
         <v>152</v>
       </c>
       <c r="C59" s="9">
@@ -9107,7 +9033,7 @@
       <c r="J67" s="9">
         <v>0</v>
       </c>
-      <c r="K67" s="33">
+      <c r="K67" s="34">
         <v>4</v>
       </c>
       <c r="L67" s="9">
@@ -14231,7 +14157,7 @@
       <c r="H158" s="12">
         <v>2</v>
       </c>
-      <c r="I158" s="34">
+      <c r="I158" s="35">
         <v>10000</v>
       </c>
       <c r="J158" s="12">
@@ -14243,7 +14169,7 @@
       <c r="L158" s="9">
         <v>350</v>
       </c>
-      <c r="M158" s="35">
+      <c r="M158" s="36">
         <v>1</v>
       </c>
       <c r="N158" s="2">
@@ -14265,8 +14191,8 @@
         <v>0</v>
       </c>
       <c r="T158" s="9"/>
-      <c r="Y158" s="36"/>
-      <c r="Z158" s="36"/>
+      <c r="Y158" s="37"/>
+      <c r="Z158" s="37"/>
     </row>
     <row r="159" spans="1:26">
       <c r="A159" s="12">
@@ -14290,7 +14216,7 @@
       <c r="H159" s="12">
         <v>2</v>
       </c>
-      <c r="I159" s="34">
+      <c r="I159" s="35">
         <v>10000</v>
       </c>
       <c r="J159" s="12">
@@ -14302,7 +14228,7 @@
       <c r="L159" s="9">
         <v>350</v>
       </c>
-      <c r="M159" s="35">
+      <c r="M159" s="36">
         <v>1</v>
       </c>
       <c r="N159" s="2">
@@ -14324,8 +14250,8 @@
         <v>0</v>
       </c>
       <c r="T159" s="9"/>
-      <c r="Y159" s="36"/>
-      <c r="Z159" s="36"/>
+      <c r="Y159" s="37"/>
+      <c r="Z159" s="37"/>
     </row>
     <row r="160" spans="1:26">
       <c r="A160" s="12">
@@ -14349,7 +14275,7 @@
       <c r="H160" s="12">
         <v>0</v>
       </c>
-      <c r="I160" s="34">
+      <c r="I160" s="35">
         <v>10000</v>
       </c>
       <c r="J160" s="12">
@@ -14361,7 +14287,7 @@
       <c r="L160" s="9">
         <v>350</v>
       </c>
-      <c r="M160" s="35">
+      <c r="M160" s="36">
         <v>2</v>
       </c>
       <c r="N160" s="2">
@@ -14408,7 +14334,7 @@
       <c r="H161" s="12">
         <v>1</v>
       </c>
-      <c r="I161" s="34">
+      <c r="I161" s="35">
         <v>10000</v>
       </c>
       <c r="J161" s="12">
@@ -14420,7 +14346,7 @@
       <c r="L161" s="9">
         <v>350</v>
       </c>
-      <c r="M161" s="35">
+      <c r="M161" s="36">
         <v>1</v>
       </c>
       <c r="N161" s="2">
@@ -14467,7 +14393,7 @@
       <c r="H162" s="12">
         <v>1</v>
       </c>
-      <c r="I162" s="34">
+      <c r="I162" s="35">
         <v>10000</v>
       </c>
       <c r="J162" s="12">
@@ -14479,7 +14405,7 @@
       <c r="L162" s="9">
         <v>350</v>
       </c>
-      <c r="M162" s="35">
+      <c r="M162" s="36">
         <v>1</v>
       </c>
       <c r="N162" s="2">
@@ -14526,7 +14452,7 @@
       <c r="H163" s="12">
         <v>0</v>
       </c>
-      <c r="I163" s="34">
+      <c r="I163" s="35">
         <v>10000</v>
       </c>
       <c r="J163" s="12">
@@ -14538,7 +14464,7 @@
       <c r="L163" s="9">
         <v>350</v>
       </c>
-      <c r="M163" s="35">
+      <c r="M163" s="36">
         <v>2</v>
       </c>
       <c r="N163" s="2">
@@ -14585,7 +14511,7 @@
       <c r="H164" s="12">
         <v>0</v>
       </c>
-      <c r="I164" s="34">
+      <c r="I164" s="35">
         <v>10000</v>
       </c>
       <c r="J164" s="12">
@@ -14597,7 +14523,7 @@
       <c r="L164" s="9">
         <v>350</v>
       </c>
-      <c r="M164" s="35">
+      <c r="M164" s="36">
         <v>2</v>
       </c>
       <c r="N164" s="2">
@@ -14644,7 +14570,7 @@
       <c r="H165" s="12">
         <v>1</v>
       </c>
-      <c r="I165" s="34">
+      <c r="I165" s="35">
         <v>10000</v>
       </c>
       <c r="J165" s="12">
@@ -14656,7 +14582,7 @@
       <c r="L165" s="9">
         <v>350</v>
       </c>
-      <c r="M165" s="35">
+      <c r="M165" s="36">
         <v>1</v>
       </c>
       <c r="N165" s="2">
@@ -14678,8 +14604,8 @@
         <v>0</v>
       </c>
       <c r="T165" s="9"/>
-      <c r="Y165" s="36"/>
-      <c r="Z165" s="36"/>
+      <c r="Y165" s="37"/>
+      <c r="Z165" s="37"/>
     </row>
     <row r="166" spans="1:26">
       <c r="A166" s="12">
@@ -14703,7 +14629,7 @@
       <c r="H166" s="12">
         <v>1</v>
       </c>
-      <c r="I166" s="34">
+      <c r="I166" s="35">
         <v>10000</v>
       </c>
       <c r="J166" s="12">
@@ -14715,7 +14641,7 @@
       <c r="L166" s="9">
         <v>350</v>
       </c>
-      <c r="M166" s="35">
+      <c r="M166" s="36">
         <v>2</v>
       </c>
       <c r="N166" s="2">
@@ -14737,8 +14663,8 @@
         <v>0</v>
       </c>
       <c r="T166"/>
-      <c r="Y166" s="36"/>
-      <c r="Z166" s="36"/>
+      <c r="Y166" s="37"/>
+      <c r="Z166" s="37"/>
     </row>
     <row r="167" spans="1:26" ht="15" customHeight="1">
       <c r="A167" s="12">
@@ -14795,8 +14721,8 @@
       <c r="S167" s="2">
         <v>0</v>
       </c>
-      <c r="Y167" s="36"/>
-      <c r="Z167" s="36"/>
+      <c r="Y167" s="37"/>
+      <c r="Z167" s="37"/>
     </row>
     <row r="168" spans="1:26">
       <c r="A168" s="12">
@@ -14853,8 +14779,8 @@
       <c r="S168" s="2">
         <v>0</v>
       </c>
-      <c r="Y168" s="36"/>
-      <c r="Z168" s="36"/>
+      <c r="Y168" s="37"/>
+      <c r="Z168" s="37"/>
     </row>
     <row r="169" spans="1:26">
       <c r="A169" s="12">
@@ -14878,7 +14804,7 @@
       <c r="H169" s="2">
         <v>0</v>
       </c>
-      <c r="I169" s="34">
+      <c r="I169" s="35">
         <v>10000</v>
       </c>
       <c r="J169" s="2">
@@ -14912,8 +14838,8 @@
         <v>0</v>
       </c>
       <c r="T169"/>
-      <c r="Y169" s="36"/>
-      <c r="Z169" s="36"/>
+      <c r="Y169" s="37"/>
+      <c r="Z169" s="37"/>
     </row>
     <row r="170" spans="1:26">
       <c r="A170" s="12">
@@ -14937,7 +14863,7 @@
       <c r="H170" s="12">
         <v>2</v>
       </c>
-      <c r="I170" s="34">
+      <c r="I170" s="35">
         <v>10000</v>
       </c>
       <c r="J170" s="12">
@@ -14949,7 +14875,7 @@
       <c r="L170" s="9">
         <v>350</v>
       </c>
-      <c r="M170" s="35">
+      <c r="M170" s="36">
         <v>1</v>
       </c>
       <c r="N170" s="2">
@@ -14971,8 +14897,8 @@
         <v>0</v>
       </c>
       <c r="T170" s="9"/>
-      <c r="Y170" s="36"/>
-      <c r="Z170" s="36"/>
+      <c r="Y170" s="37"/>
+      <c r="Z170" s="37"/>
     </row>
     <row r="171" spans="1:26">
       <c r="A171" s="12">
@@ -14996,7 +14922,7 @@
       <c r="H171" s="12">
         <v>2</v>
       </c>
-      <c r="I171" s="34">
+      <c r="I171" s="35">
         <v>10000</v>
       </c>
       <c r="J171" s="12">
@@ -15008,7 +14934,7 @@
       <c r="L171" s="9">
         <v>350</v>
       </c>
-      <c r="M171" s="35">
+      <c r="M171" s="36">
         <v>1</v>
       </c>
       <c r="N171" s="2">
@@ -15030,8 +14956,8 @@
         <v>0</v>
       </c>
       <c r="T171" s="9"/>
-      <c r="Y171" s="36"/>
-      <c r="Z171" s="36"/>
+      <c r="Y171" s="37"/>
+      <c r="Z171" s="37"/>
     </row>
     <row r="172" spans="1:26">
       <c r="A172" s="12">
@@ -15055,7 +14981,7 @@
       <c r="H172" s="12">
         <v>1</v>
       </c>
-      <c r="I172" s="34">
+      <c r="I172" s="35">
         <v>10000</v>
       </c>
       <c r="J172" s="12">
@@ -15067,7 +14993,7 @@
       <c r="L172" s="9">
         <v>350</v>
       </c>
-      <c r="M172" s="35">
+      <c r="M172" s="36">
         <v>1</v>
       </c>
       <c r="N172" s="2">
@@ -15089,8 +15015,8 @@
         <v>0</v>
       </c>
       <c r="T172" s="9"/>
-      <c r="Y172" s="36"/>
-      <c r="Z172" s="36"/>
+      <c r="Y172" s="37"/>
+      <c r="Z172" s="37"/>
     </row>
     <row r="173" spans="1:26">
       <c r="A173" s="12">
@@ -15114,7 +15040,7 @@
       <c r="H173" s="12">
         <v>1</v>
       </c>
-      <c r="I173" s="34">
+      <c r="I173" s="35">
         <v>10000</v>
       </c>
       <c r="J173" s="12">
@@ -15126,7 +15052,7 @@
       <c r="L173" s="9">
         <v>350</v>
       </c>
-      <c r="M173" s="35">
+      <c r="M173" s="36">
         <v>1</v>
       </c>
       <c r="N173" s="2">
@@ -15148,8 +15074,8 @@
         <v>0</v>
       </c>
       <c r="T173" s="9"/>
-      <c r="Y173" s="36"/>
-      <c r="Z173" s="36"/>
+      <c r="Y173" s="37"/>
+      <c r="Z173" s="37"/>
     </row>
     <row r="174" spans="1:26">
       <c r="A174" s="12">
@@ -15173,7 +15099,7 @@
       <c r="H174" s="12">
         <v>2</v>
       </c>
-      <c r="I174" s="34">
+      <c r="I174" s="35">
         <v>10000</v>
       </c>
       <c r="J174" s="12">
@@ -15185,7 +15111,7 @@
       <c r="L174" s="9">
         <v>350</v>
       </c>
-      <c r="M174" s="35">
+      <c r="M174" s="36">
         <v>1</v>
       </c>
       <c r="N174" s="2">
@@ -15207,8 +15133,8 @@
         <v>0</v>
       </c>
       <c r="T174" s="9"/>
-      <c r="Y174" s="36"/>
-      <c r="Z174" s="36"/>
+      <c r="Y174" s="37"/>
+      <c r="Z174" s="37"/>
     </row>
     <row r="175" spans="1:26">
       <c r="A175" s="12">
@@ -15232,7 +15158,7 @@
       <c r="H175" s="12">
         <v>1</v>
       </c>
-      <c r="I175" s="34">
+      <c r="I175" s="35">
         <v>10000</v>
       </c>
       <c r="J175" s="12">
@@ -15244,7 +15170,7 @@
       <c r="L175" s="9">
         <v>350</v>
       </c>
-      <c r="M175" s="35">
+      <c r="M175" s="36">
         <v>1</v>
       </c>
       <c r="N175" s="2">
@@ -15266,8 +15192,8 @@
         <v>0</v>
       </c>
       <c r="T175" s="9"/>
-      <c r="Y175" s="36"/>
-      <c r="Z175" s="36"/>
+      <c r="Y175" s="37"/>
+      <c r="Z175" s="37"/>
     </row>
     <row r="176" spans="1:26">
       <c r="A176" s="2">
@@ -15386,9 +15312,6 @@
       <c r="S177" s="2">
         <v>0</v>
       </c>
-      <c r="U177" s="2">
-        <v>1</v>
-      </c>
       <c r="Y177" s="11"/>
       <c r="Z177" s="11"/>
     </row>
@@ -15414,7 +15337,7 @@
       <c r="H178" s="2">
         <v>1</v>
       </c>
-      <c r="I178" s="34">
+      <c r="I178" s="35">
         <v>10000</v>
       </c>
       <c r="J178" s="2">
@@ -15921,30 +15844,27 @@
       <c r="S186" s="2">
         <v>0</v>
       </c>
-      <c r="U186" s="2">
-        <v>1</v>
-      </c>
       <c r="Y186" s="11"/>
       <c r="Z186" s="11"/>
     </row>
     <row r="187" spans="1:26" s="10" customFormat="1">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="10">
+        <v>1014025</v>
+      </c>
+      <c r="B187" s="37" t="s">
         <v>344</v>
       </c>
-      <c r="B187" s="36" t="s">
+      <c r="C187" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G187" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="C187" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D187" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E187" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G187" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="H187" s="10" t="s">
         <v>91</v>
@@ -15982,7 +15902,7 @@
       <c r="S187" s="10">
         <v>0</v>
       </c>
-      <c r="W187" s="37"/>
+      <c r="W187" s="38"/>
       <c r="Y187" s="11"/>
       <c r="Z187" s="11"/>
     </row>
@@ -15990,8 +15910,8 @@
       <c r="A188" s="10">
         <v>1014029</v>
       </c>
-      <c r="B188" s="36" t="s">
-        <v>347</v>
+      <c r="B188" s="37" t="s">
+        <v>346</v>
       </c>
       <c r="H188" s="10">
         <v>1</v>
@@ -16029,7 +15949,7 @@
       <c r="S188" s="10">
         <v>0</v>
       </c>
-      <c r="W188" s="37"/>
+      <c r="W188" s="38"/>
       <c r="Y188" s="7"/>
       <c r="Z188" s="7"/>
     </row>
@@ -16037,8 +15957,8 @@
       <c r="A189" s="10">
         <v>1014030</v>
       </c>
-      <c r="B189" s="38" t="s">
-        <v>348</v>
+      <c r="B189" s="39" t="s">
+        <v>347</v>
       </c>
       <c r="C189" s="10">
         <v>0</v>
@@ -16088,7 +16008,7 @@
       <c r="S189" s="9">
         <v>0</v>
       </c>
-      <c r="W189" s="37"/>
+      <c r="W189" s="38"/>
       <c r="Y189" s="7"/>
       <c r="Z189" s="7"/>
     </row>
@@ -16096,8 +16016,8 @@
       <c r="A190" s="10">
         <v>1014031</v>
       </c>
-      <c r="B190" s="38" t="s">
-        <v>349</v>
+      <c r="B190" s="39" t="s">
+        <v>348</v>
       </c>
       <c r="C190" s="10">
         <v>0</v>
@@ -16147,7 +16067,7 @@
       <c r="S190" s="9">
         <v>0</v>
       </c>
-      <c r="W190" s="37"/>
+      <c r="W190" s="38"/>
       <c r="Y190" s="7"/>
       <c r="Z190" s="7"/>
     </row>
@@ -16155,8 +16075,8 @@
       <c r="A191" s="10">
         <v>1014032</v>
       </c>
-      <c r="B191" s="39" t="s">
-        <v>350</v>
+      <c r="B191" s="40" t="s">
+        <v>349</v>
       </c>
       <c r="C191" s="10">
         <v>0</v>
@@ -16206,14 +16126,14 @@
       <c r="S191" s="9">
         <v>0</v>
       </c>
-      <c r="W191" s="37"/>
+      <c r="W191" s="38"/>
     </row>
     <row r="192" spans="1:26" s="10" customFormat="1">
       <c r="A192" s="10">
         <v>1014033</v>
       </c>
-      <c r="B192" s="39" t="s">
-        <v>351</v>
+      <c r="B192" s="40" t="s">
+        <v>350</v>
       </c>
       <c r="C192" s="10">
         <v>0</v>
@@ -16263,14 +16183,14 @@
       <c r="S192" s="9">
         <v>0</v>
       </c>
-      <c r="W192" s="37"/>
+      <c r="W192" s="38"/>
     </row>
     <row r="193" spans="1:26" s="10" customFormat="1">
       <c r="A193" s="10">
         <v>1014034</v>
       </c>
-      <c r="B193" s="39" t="s">
-        <v>352</v>
+      <c r="B193" s="40" t="s">
+        <v>351</v>
       </c>
       <c r="C193" s="10">
         <v>0</v>
@@ -16320,7 +16240,7 @@
       <c r="S193" s="9">
         <v>0</v>
       </c>
-      <c r="W193" s="37"/>
+      <c r="W193" s="38"/>
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
@@ -16328,8 +16248,8 @@
       <c r="A194" s="10">
         <v>1014011</v>
       </c>
-      <c r="B194" s="36" t="s">
-        <v>353</v>
+      <c r="B194" s="37" t="s">
+        <v>352</v>
       </c>
       <c r="C194" s="10">
         <v>0</v>
@@ -16382,7 +16302,7 @@
       <c r="S194" s="9">
         <v>0</v>
       </c>
-      <c r="W194" s="37"/>
+      <c r="W194" s="38"/>
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
@@ -16390,8 +16310,8 @@
       <c r="A195" s="10">
         <v>1014016</v>
       </c>
-      <c r="B195" s="39" t="s">
-        <v>354</v>
+      <c r="B195" s="40" t="s">
+        <v>353</v>
       </c>
       <c r="C195" s="10">
         <v>0</v>
@@ -16441,7 +16361,7 @@
       <c r="S195" s="9">
         <v>0</v>
       </c>
-      <c r="W195" s="37"/>
+      <c r="W195" s="38"/>
       <c r="Y195"/>
       <c r="Z195"/>
     </row>
@@ -16449,8 +16369,8 @@
       <c r="A196" s="10">
         <v>1014019</v>
       </c>
-      <c r="B196" s="36" t="s">
-        <v>355</v>
+      <c r="B196" s="37" t="s">
+        <v>354</v>
       </c>
       <c r="C196" s="10">
         <v>0</v>
@@ -16503,7 +16423,7 @@
       <c r="S196" s="9">
         <v>0</v>
       </c>
-      <c r="W196" s="37"/>
+      <c r="W196" s="38"/>
       <c r="Y196"/>
       <c r="Z196"/>
     </row>
@@ -16511,8 +16431,8 @@
       <c r="A197" s="10">
         <v>1014020</v>
       </c>
-      <c r="B197" s="36" t="s">
-        <v>356</v>
+      <c r="B197" s="37" t="s">
+        <v>355</v>
       </c>
       <c r="C197" s="10">
         <v>0</v>
@@ -16565,7 +16485,7 @@
       <c r="S197" s="9">
         <v>0</v>
       </c>
-      <c r="W197" s="37"/>
+      <c r="W197" s="38"/>
       <c r="Y197"/>
       <c r="Z197"/>
     </row>
@@ -16573,8 +16493,8 @@
       <c r="A198" s="10">
         <v>1014021</v>
       </c>
-      <c r="B198" s="36" t="s">
-        <v>357</v>
+      <c r="B198" s="37" t="s">
+        <v>356</v>
       </c>
       <c r="C198" s="10">
         <v>0</v>
@@ -16624,7 +16544,7 @@
       <c r="S198" s="9">
         <v>0</v>
       </c>
-      <c r="W198" s="37"/>
+      <c r="W198" s="38"/>
       <c r="Y198"/>
       <c r="Z198"/>
     </row>
@@ -16632,8 +16552,8 @@
       <c r="A199" s="10">
         <v>1014022</v>
       </c>
-      <c r="B199" s="36" t="s">
-        <v>358</v>
+      <c r="B199" s="37" t="s">
+        <v>357</v>
       </c>
       <c r="C199" s="10">
         <v>0</v>
@@ -16683,7 +16603,7 @@
       <c r="S199" s="9">
         <v>0</v>
       </c>
-      <c r="W199" s="37"/>
+      <c r="W199" s="38"/>
       <c r="Y199"/>
       <c r="Z199"/>
     </row>
@@ -16691,8 +16611,8 @@
       <c r="A200" s="10">
         <v>1014023</v>
       </c>
-      <c r="B200" s="36" t="s">
-        <v>359</v>
+      <c r="B200" s="37" t="s">
+        <v>358</v>
       </c>
       <c r="C200" s="10">
         <v>0</v>
@@ -16742,7 +16662,7 @@
       <c r="S200" s="9">
         <v>0</v>
       </c>
-      <c r="W200" s="37"/>
+      <c r="W200" s="38"/>
       <c r="Y200"/>
       <c r="Z200"/>
     </row>
@@ -16750,8 +16670,8 @@
       <c r="A201" s="10">
         <v>1014024</v>
       </c>
-      <c r="B201" s="36" t="s">
-        <v>360</v>
+      <c r="B201" s="37" t="s">
+        <v>359</v>
       </c>
       <c r="C201" s="10">
         <v>0</v>
@@ -16801,7 +16721,7 @@
       <c r="S201" s="9">
         <v>0</v>
       </c>
-      <c r="W201" s="37"/>
+      <c r="W201" s="38"/>
       <c r="Y201"/>
       <c r="Z201"/>
     </row>
@@ -16809,17 +16729,20 @@
       <c r="A202" s="10">
         <v>1014000</v>
       </c>
-      <c r="B202" s="36" t="s">
-        <v>361</v>
-      </c>
-      <c r="C202" s="10" t="s">
-        <v>89</v>
+      <c r="B202" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="C202" s="2">
+        <v>0</v>
       </c>
       <c r="D202" s="10">
         <v>4</v>
       </c>
-      <c r="E202" s="10">
-        <v>1</v>
+      <c r="E202" s="9">
+        <v>0</v>
+      </c>
+      <c r="F202" s="10">
+        <v>0</v>
       </c>
       <c r="G202" s="10">
         <v>1</v>
@@ -16860,7 +16783,11 @@
       <c r="S202" s="10">
         <v>0</v>
       </c>
-      <c r="W202" s="37"/>
+      <c r="U202" s="9">
+        <v>1</v>
+      </c>
+      <c r="V202" s="9"/>
+      <c r="W202" s="38"/>
       <c r="Y202"/>
       <c r="Z202"/>
     </row>
@@ -16868,8 +16795,8 @@
       <c r="A203" s="10">
         <v>1014028</v>
       </c>
-      <c r="B203" s="39" t="s">
-        <v>362</v>
+      <c r="B203" s="40" t="s">
+        <v>361</v>
       </c>
       <c r="C203" s="10">
         <v>0</v>
@@ -16878,7 +16805,7 @@
         <v>89</v>
       </c>
       <c r="E203" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G203" s="10">
         <v>17</v>
@@ -16916,7 +16843,7 @@
       <c r="R203" s="10">
         <v>0</v>
       </c>
-      <c r="W203" s="37"/>
+      <c r="W203" s="38"/>
       <c r="Y203"/>
       <c r="Z203"/>
     </row>
@@ -16924,8 +16851,8 @@
       <c r="A204" s="10">
         <v>1400001</v>
       </c>
-      <c r="B204" s="39" t="s">
-        <v>363</v>
+      <c r="B204" s="40" t="s">
+        <v>362</v>
       </c>
       <c r="C204" s="10">
         <v>1</v>
@@ -16972,7 +16899,7 @@
       <c r="S204" s="10">
         <v>0</v>
       </c>
-      <c r="W204" s="37"/>
+      <c r="W204" s="38"/>
       <c r="Y204"/>
       <c r="Z204"/>
     </row>
@@ -16980,8 +16907,8 @@
       <c r="A205" s="11">
         <v>1016005</v>
       </c>
-      <c r="B205" s="40" t="s">
-        <v>354</v>
+      <c r="B205" s="41" t="s">
+        <v>353</v>
       </c>
       <c r="C205" s="11">
         <v>0</v>
@@ -17001,7 +16928,7 @@
       <c r="H205" s="11">
         <v>2</v>
       </c>
-      <c r="I205" s="41">
+      <c r="I205" s="42">
         <v>10000</v>
       </c>
       <c r="J205" s="11">
@@ -17034,7 +16961,7 @@
       <c r="S205" s="11">
         <v>0</v>
       </c>
-      <c r="W205" s="42"/>
+      <c r="W205" s="43"/>
       <c r="Y205"/>
       <c r="Z205"/>
     </row>
@@ -17042,8 +16969,8 @@
       <c r="A206" s="11">
         <v>1016006</v>
       </c>
-      <c r="B206" s="40" t="s">
-        <v>364</v>
+      <c r="B206" s="41" t="s">
+        <v>363</v>
       </c>
       <c r="C206" s="11">
         <v>0</v>
@@ -17063,7 +16990,7 @@
       <c r="H206" s="11">
         <v>0</v>
       </c>
-      <c r="I206" s="41">
+      <c r="I206" s="42">
         <v>10000</v>
       </c>
       <c r="J206" s="11">
@@ -17093,13 +17020,7 @@
       <c r="S206" s="11">
         <v>1</v>
       </c>
-      <c r="U206" s="11">
-        <v>1</v>
-      </c>
-      <c r="V206" s="11">
-        <v>1</v>
-      </c>
-      <c r="W206" s="42"/>
+      <c r="W206" s="43"/>
       <c r="Y206"/>
       <c r="Z206"/>
     </row>
@@ -17107,8 +17028,8 @@
       <c r="A207" s="11">
         <v>1016007</v>
       </c>
-      <c r="B207" s="40" t="s">
-        <v>365</v>
+      <c r="B207" s="41" t="s">
+        <v>364</v>
       </c>
       <c r="C207" s="11">
         <v>0</v>
@@ -17128,7 +17049,7 @@
       <c r="H207" s="11">
         <v>2</v>
       </c>
-      <c r="I207" s="41">
+      <c r="I207" s="42">
         <v>10000</v>
       </c>
       <c r="J207" s="11">
@@ -17161,7 +17082,7 @@
       <c r="S207" s="11">
         <v>1</v>
       </c>
-      <c r="W207" s="42"/>
+      <c r="W207" s="43"/>
       <c r="Y207"/>
       <c r="Z207"/>
     </row>
@@ -17169,8 +17090,8 @@
       <c r="A208" s="11">
         <v>1016008</v>
       </c>
-      <c r="B208" s="40" t="s">
-        <v>366</v>
+      <c r="B208" s="41" t="s">
+        <v>365</v>
       </c>
       <c r="C208" s="11">
         <v>0</v>
@@ -17190,7 +17111,7 @@
       <c r="H208" s="11">
         <v>2</v>
       </c>
-      <c r="I208" s="41">
+      <c r="I208" s="42">
         <v>10000</v>
       </c>
       <c r="J208" s="11">
@@ -17223,7 +17144,7 @@
       <c r="S208" s="11">
         <v>1</v>
       </c>
-      <c r="W208" s="42"/>
+      <c r="W208" s="43"/>
       <c r="Y208"/>
       <c r="Z208"/>
     </row>
@@ -17231,8 +17152,8 @@
       <c r="A209" s="11">
         <v>1016009</v>
       </c>
-      <c r="B209" s="40" t="s">
-        <v>367</v>
+      <c r="B209" s="41" t="s">
+        <v>366</v>
       </c>
       <c r="C209" s="11">
         <v>0</v>
@@ -17252,7 +17173,7 @@
       <c r="H209" s="11">
         <v>2</v>
       </c>
-      <c r="I209" s="41">
+      <c r="I209" s="42">
         <v>10000</v>
       </c>
       <c r="J209" s="11">
@@ -17285,7 +17206,7 @@
       <c r="S209" s="9">
         <v>1</v>
       </c>
-      <c r="W209" s="42"/>
+      <c r="W209" s="43"/>
       <c r="Y209"/>
       <c r="Z209"/>
     </row>
@@ -17293,8 +17214,8 @@
       <c r="A210" s="11">
         <v>1016010</v>
       </c>
-      <c r="B210" s="40" t="s">
-        <v>368</v>
+      <c r="B210" s="41" t="s">
+        <v>367</v>
       </c>
       <c r="C210" s="11">
         <v>0</v>
@@ -17314,7 +17235,7 @@
       <c r="H210" s="11">
         <v>2</v>
       </c>
-      <c r="I210" s="41">
+      <c r="I210" s="42">
         <v>10000</v>
       </c>
       <c r="J210" s="11">
@@ -17347,7 +17268,7 @@
       <c r="S210" s="9">
         <v>1</v>
       </c>
-      <c r="W210" s="42"/>
+      <c r="W210" s="43"/>
       <c r="Y210"/>
       <c r="Z210"/>
     </row>
@@ -17355,8 +17276,8 @@
       <c r="A211" s="11">
         <v>1016011</v>
       </c>
-      <c r="B211" s="40" t="s">
-        <v>360</v>
+      <c r="B211" s="41" t="s">
+        <v>359</v>
       </c>
       <c r="C211" s="11">
         <v>0</v>
@@ -17376,7 +17297,7 @@
       <c r="H211" s="11">
         <v>2</v>
       </c>
-      <c r="I211" s="41">
+      <c r="I211" s="42">
         <v>10000</v>
       </c>
       <c r="J211" s="11">
@@ -17409,7 +17330,7 @@
       <c r="S211" s="9">
         <v>0</v>
       </c>
-      <c r="W211" s="42"/>
+      <c r="W211" s="43"/>
       <c r="Y211"/>
       <c r="Z211"/>
     </row>
@@ -17417,8 +17338,8 @@
       <c r="A212" s="11">
         <v>1016012</v>
       </c>
-      <c r="B212" s="40" t="s">
-        <v>369</v>
+      <c r="B212" s="41" t="s">
+        <v>368</v>
       </c>
       <c r="C212" s="11">
         <v>0</v>
@@ -17438,7 +17359,7 @@
       <c r="H212" s="11">
         <v>2</v>
       </c>
-      <c r="I212" s="41">
+      <c r="I212" s="42">
         <v>10000</v>
       </c>
       <c r="J212" s="11">
@@ -17471,7 +17392,7 @@
       <c r="S212" s="9">
         <v>1</v>
       </c>
-      <c r="W212" s="42"/>
+      <c r="W212" s="43"/>
       <c r="Y212"/>
       <c r="Z212"/>
     </row>
@@ -17479,8 +17400,8 @@
       <c r="A213" s="11">
         <v>1016013</v>
       </c>
-      <c r="B213" s="40" t="s">
-        <v>370</v>
+      <c r="B213" s="41" t="s">
+        <v>369</v>
       </c>
       <c r="C213" s="11">
         <v>0</v>
@@ -17497,7 +17418,7 @@
       <c r="G213" s="11">
         <v>13</v>
       </c>
-      <c r="I213" s="41">
+      <c r="I213" s="42">
         <v>10000</v>
       </c>
       <c r="J213" s="11">
@@ -17527,13 +17448,7 @@
       <c r="S213" s="11">
         <v>1</v>
       </c>
-      <c r="U213" s="11">
-        <v>1</v>
-      </c>
-      <c r="V213" s="11">
-        <v>1</v>
-      </c>
-      <c r="W213" s="42"/>
+      <c r="W213" s="43"/>
       <c r="Y213"/>
       <c r="Z213"/>
     </row>
@@ -17541,8 +17456,8 @@
       <c r="A214" s="11">
         <v>1016014</v>
       </c>
-      <c r="B214" s="40" t="s">
-        <v>371</v>
+      <c r="B214" s="41" t="s">
+        <v>370</v>
       </c>
       <c r="C214" s="11">
         <v>0</v>
@@ -17562,7 +17477,7 @@
       <c r="H214" s="11">
         <v>2</v>
       </c>
-      <c r="I214" s="41">
+      <c r="I214" s="42">
         <v>10000</v>
       </c>
       <c r="J214" s="11">
@@ -17595,7 +17510,7 @@
       <c r="S214" s="9">
         <v>1</v>
       </c>
-      <c r="W214" s="42"/>
+      <c r="W214" s="43"/>
       <c r="Y214"/>
       <c r="Z214"/>
     </row>
@@ -17603,7 +17518,7 @@
       <c r="A215" s="11">
         <v>1016015</v>
       </c>
-      <c r="B215" s="40" t="s">
+      <c r="B215" s="41" t="s">
         <v>341</v>
       </c>
       <c r="C215" s="11">
@@ -17624,7 +17539,7 @@
       <c r="H215" s="11">
         <v>0</v>
       </c>
-      <c r="I215" s="41">
+      <c r="I215" s="42">
         <v>10000</v>
       </c>
       <c r="J215" s="11">
@@ -17654,7 +17569,7 @@
       <c r="S215" s="11">
         <v>1</v>
       </c>
-      <c r="W215" s="42"/>
+      <c r="W215" s="43"/>
       <c r="Y215"/>
       <c r="Z215"/>
     </row>
@@ -17662,8 +17577,8 @@
       <c r="A216" s="11">
         <v>1016016</v>
       </c>
-      <c r="B216" s="40" t="s">
-        <v>372</v>
+      <c r="B216" s="41" t="s">
+        <v>371</v>
       </c>
       <c r="C216" s="11">
         <v>0</v>
@@ -17683,7 +17598,7 @@
       <c r="H216" s="11">
         <v>2</v>
       </c>
-      <c r="I216" s="41">
+      <c r="I216" s="42">
         <v>10000</v>
       </c>
       <c r="J216" s="11">
@@ -17713,7 +17628,7 @@
       <c r="S216" s="11">
         <v>1</v>
       </c>
-      <c r="W216" s="42"/>
+      <c r="W216" s="43"/>
       <c r="Y216"/>
       <c r="Z216"/>
     </row>
@@ -17722,9 +17637,9 @@
         <v>1016017</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="I217" s="34"/>
+        <v>372</v>
+      </c>
+      <c r="I217" s="35"/>
       <c r="J217" s="11">
         <v>1</v>
       </c>
@@ -17757,7 +17672,7 @@
       </c>
       <c r="T217" s="11"/>
       <c r="U217" s="11"/>
-      <c r="W217" s="42"/>
+      <c r="W217" s="43"/>
       <c r="Y217"/>
       <c r="Z217"/>
     </row>
@@ -17766,9 +17681,9 @@
         <v>1016018</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="I218" s="34"/>
+        <v>373</v>
+      </c>
+      <c r="I218" s="35"/>
       <c r="J218" s="11">
         <v>1</v>
       </c>
@@ -17800,7 +17715,7 @@
         <v>1</v>
       </c>
       <c r="T218" s="11"/>
-      <c r="W218" s="42"/>
+      <c r="W218" s="43"/>
       <c r="Y218"/>
       <c r="Z218"/>
     </row>
@@ -17809,9 +17724,9 @@
         <v>1016019</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="I219" s="34"/>
+        <v>374</v>
+      </c>
+      <c r="I219" s="35"/>
       <c r="J219" s="11">
         <v>1</v>
       </c>
@@ -17843,7 +17758,7 @@
         <v>1</v>
       </c>
       <c r="T219" s="11"/>
-      <c r="W219" s="42"/>
+      <c r="W219" s="43"/>
       <c r="Y219"/>
       <c r="Z219"/>
     </row>
@@ -17851,8 +17766,8 @@
       <c r="A220" s="10">
         <v>1014014</v>
       </c>
-      <c r="B220" s="38" t="s">
-        <v>376</v>
+      <c r="B220" s="39" t="s">
+        <v>375</v>
       </c>
       <c r="C220" s="10">
         <v>0</v>
@@ -17887,10 +17802,10 @@
       <c r="M220" s="15">
         <v>1</v>
       </c>
-      <c r="N220" s="43">
+      <c r="N220" s="44">
         <v>7</v>
       </c>
-      <c r="O220" s="43">
+      <c r="O220" s="44">
         <v>5</v>
       </c>
       <c r="P220" s="10">
@@ -17905,7 +17820,7 @@
       <c r="S220" s="9">
         <v>1</v>
       </c>
-      <c r="W220" s="37"/>
+      <c r="W220" s="38"/>
       <c r="Y220"/>
       <c r="Z220"/>
     </row>
@@ -17914,7 +17829,7 @@
         <v>1014026</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C221" s="10">
         <v>0</v>
@@ -17949,10 +17864,10 @@
       <c r="M221" s="15">
         <v>1</v>
       </c>
-      <c r="N221" s="43">
+      <c r="N221" s="44">
         <v>7</v>
       </c>
-      <c r="O221" s="43">
+      <c r="O221" s="44">
         <v>7</v>
       </c>
       <c r="P221" s="10">
@@ -17967,7 +17882,7 @@
       <c r="S221" s="9">
         <v>1</v>
       </c>
-      <c r="W221" s="37"/>
+      <c r="W221" s="38"/>
       <c r="Y221"/>
       <c r="Z221"/>
     </row>
@@ -17976,7 +17891,7 @@
         <v>1005001</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
@@ -18024,7 +17939,7 @@
         <v>2</v>
       </c>
       <c r="R222" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="S222" s="9">
         <v>1</v>
@@ -18037,7 +17952,7 @@
         <v>1005002</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
@@ -18094,11 +18009,11 @@
       <c r="U223" s="10"/>
     </row>
     <row r="224" spans="1:26" s="13" customFormat="1">
-      <c r="A224" s="44">
+      <c r="A224" s="45">
         <v>1020068</v>
       </c>
-      <c r="B224" s="45" t="s">
-        <v>380</v>
+      <c r="B224" s="46" t="s">
+        <v>379</v>
       </c>
       <c r="C224" s="13" t="s">
         <v>89</v>
@@ -18115,7 +18030,7 @@
       <c r="H224" s="13">
         <v>1</v>
       </c>
-      <c r="I224" s="46">
+      <c r="I224" s="47">
         <v>3500</v>
       </c>
       <c r="J224" s="13">
@@ -18153,11 +18068,11 @@
       <c r="Z224"/>
     </row>
     <row r="225" spans="1:26" s="13" customFormat="1">
-      <c r="A225" s="44">
+      <c r="A225" s="45">
         <v>1020070</v>
       </c>
-      <c r="B225" s="45" t="s">
-        <v>381</v>
+      <c r="B225" s="46" t="s">
+        <v>380</v>
       </c>
       <c r="C225" s="13" t="s">
         <v>89</v>
@@ -18174,7 +18089,7 @@
       <c r="H225" s="13">
         <v>1</v>
       </c>
-      <c r="I225" s="46">
+      <c r="I225" s="47">
         <v>3500</v>
       </c>
       <c r="J225" s="13">
@@ -18212,11 +18127,11 @@
       <c r="Z225"/>
     </row>
     <row r="226" spans="1:26" s="13" customFormat="1">
-      <c r="A226" s="44">
+      <c r="A226" s="45">
         <v>1020071</v>
       </c>
-      <c r="B226" s="45" t="s">
-        <v>382</v>
+      <c r="B226" s="46" t="s">
+        <v>381</v>
       </c>
       <c r="C226" s="13" t="s">
         <v>89</v>
@@ -18233,7 +18148,7 @@
       <c r="H226" s="13">
         <v>1</v>
       </c>
-      <c r="I226" s="46">
+      <c r="I226" s="47">
         <v>3500</v>
       </c>
       <c r="J226" s="13">
@@ -18271,11 +18186,11 @@
       <c r="Z226"/>
     </row>
     <row r="227" spans="1:26" s="13" customFormat="1">
-      <c r="A227" s="44">
+      <c r="A227" s="45">
         <v>1020069</v>
       </c>
-      <c r="B227" s="45" t="s">
-        <v>383</v>
+      <c r="B227" s="46" t="s">
+        <v>382</v>
       </c>
       <c r="C227" s="13" t="s">
         <v>89</v>
@@ -18292,7 +18207,7 @@
       <c r="H227" s="13">
         <v>1</v>
       </c>
-      <c r="I227" s="46">
+      <c r="I227" s="47">
         <v>3500</v>
       </c>
       <c r="J227" s="13">
@@ -18330,11 +18245,11 @@
       <c r="Z227"/>
     </row>
     <row r="228" spans="1:26">
-      <c r="A228" s="47">
+      <c r="A228" s="48">
         <v>1014009</v>
       </c>
-      <c r="B228" s="48" t="s">
-        <v>384</v>
+      <c r="B228" s="49" t="s">
+        <v>383</v>
       </c>
       <c r="C228" s="2">
         <v>0</v>
@@ -18389,11 +18304,11 @@
       </c>
     </row>
     <row r="229" spans="1:26">
-      <c r="A229" s="47">
+      <c r="A229" s="48">
         <v>1005003</v>
       </c>
-      <c r="B229" s="48" t="s">
-        <v>385</v>
+      <c r="B229" s="49" t="s">
+        <v>384</v>
       </c>
       <c r="C229" s="2">
         <v>0</v>
@@ -18454,7 +18369,7 @@
         <v>1005005</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C230" s="2">
         <v>0</v>
@@ -18514,7 +18429,10 @@
         <v>1011000</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
+      </c>
+      <c r="C231" s="2">
+        <v>0</v>
       </c>
       <c r="D231" s="2">
         <v>4</v>
@@ -18522,6 +18440,9 @@
       <c r="E231" s="2">
         <v>0</v>
       </c>
+      <c r="F231" s="2">
+        <v>0</v>
+      </c>
       <c r="G231" s="2" t="s">
         <v>89</v>
       </c>
@@ -18559,6 +18480,12 @@
         <v>1</v>
       </c>
       <c r="S231" s="2">
+        <v>1</v>
+      </c>
+      <c r="U231" s="9">
+        <v>1</v>
+      </c>
+      <c r="V231" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18567,10 +18494,10 @@
         <v>1012000</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>89</v>
+        <v>387</v>
+      </c>
+      <c r="C232" s="2">
+        <v>0</v>
       </c>
       <c r="D232" s="2">
         <v>4</v>
@@ -18578,6 +18505,9 @@
       <c r="E232" s="2">
         <v>0</v>
       </c>
+      <c r="F232" s="2">
+        <v>0</v>
+      </c>
       <c r="G232" s="2">
         <v>1</v>
       </c>
@@ -18615,6 +18545,12 @@
         <v>1</v>
       </c>
       <c r="S232" s="2">
+        <v>1</v>
+      </c>
+      <c r="U232" s="9">
+        <v>1</v>
+      </c>
+      <c r="V232" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18623,10 +18559,10 @@
         <v>1015000</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>89</v>
+        <v>388</v>
+      </c>
+      <c r="C233" s="2">
+        <v>0</v>
       </c>
       <c r="D233" s="2">
         <v>4</v>
@@ -18634,6 +18570,9 @@
       <c r="E233" s="2">
         <v>0</v>
       </c>
+      <c r="F233" s="2">
+        <v>0</v>
+      </c>
       <c r="G233" s="2">
         <v>1</v>
       </c>
@@ -18671,6 +18610,12 @@
         <v>1</v>
       </c>
       <c r="S233" s="2">
+        <v>1</v>
+      </c>
+      <c r="U233" s="9">
+        <v>1</v>
+      </c>
+      <c r="V233" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18679,10 +18624,10 @@
         <v>1016000</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>89</v>
+        <v>389</v>
+      </c>
+      <c r="C234" s="2">
+        <v>0</v>
       </c>
       <c r="D234" s="2">
         <v>4</v>
@@ -18690,6 +18635,9 @@
       <c r="E234" s="2">
         <v>0</v>
       </c>
+      <c r="F234" s="2">
+        <v>0</v>
+      </c>
       <c r="G234" s="2">
         <v>1</v>
       </c>
@@ -18727,6 +18675,12 @@
         <v>1</v>
       </c>
       <c r="S234" s="2">
+        <v>1</v>
+      </c>
+      <c r="U234" s="9">
+        <v>1</v>
+      </c>
+      <c r="V234" s="9">
         <v>1</v>
       </c>
     </row>
@@ -18735,7 +18689,7 @@
         <v>1007001</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
@@ -18744,7 +18698,7 @@
         <v>0</v>
       </c>
       <c r="E235" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F235" s="2">
         <v>1</v>
@@ -18794,7 +18748,7 @@
         <v>1007002</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C236" s="9">
         <v>0</v>
@@ -18803,7 +18757,7 @@
         <v>0</v>
       </c>
       <c r="E236" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F236" s="9">
         <v>1</v>
@@ -18857,7 +18811,7 @@
         <v>1007003</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C237" s="9">
         <v>0</v>
@@ -18866,7 +18820,7 @@
         <v>0</v>
       </c>
       <c r="E237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F237" s="9">
         <v>1</v>
@@ -18920,7 +18874,7 @@
         <v>1005006</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C238" s="9">
         <v>0</v>
@@ -18952,7 +18906,7 @@
       <c r="L238" s="9">
         <v>350</v>
       </c>
-      <c r="M238" s="31">
+      <c r="M238" s="32">
         <v>2</v>
       </c>
       <c r="N238" s="9">
@@ -18975,86 +18929,210 @@
       <c r="Y238"/>
       <c r="Z238"/>
     </row>
+    <row r="239" spans="1:26">
+      <c r="A239" s="2">
+        <v>1005007</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C239" s="2">
+        <v>0</v>
+      </c>
+      <c r="D239" s="2">
+        <v>3</v>
+      </c>
+      <c r="E239" s="2">
+        <v>1</v>
+      </c>
+      <c r="F239" s="2">
+        <v>1</v>
+      </c>
+      <c r="G239" s="2">
+        <v>1</v>
+      </c>
+      <c r="H239" s="2">
+        <v>0</v>
+      </c>
+      <c r="I239" s="14">
+        <v>10000</v>
+      </c>
+      <c r="J239" s="2">
+        <v>0</v>
+      </c>
+      <c r="K239" s="2">
+        <v>8</v>
+      </c>
+      <c r="L239" s="2">
+        <v>350</v>
+      </c>
+      <c r="M239" s="15">
+        <v>2</v>
+      </c>
+      <c r="N239" s="2">
+        <v>1</v>
+      </c>
+      <c r="O239" s="2">
+        <v>1</v>
+      </c>
+      <c r="P239" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q239" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="S239" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:26" s="9" customFormat="1" ht="16.5">
+      <c r="A240" s="2">
+        <v>1007004</v>
+      </c>
+      <c r="B240" s="50" t="s">
+        <v>395</v>
+      </c>
+      <c r="C240" s="9">
+        <v>0</v>
+      </c>
+      <c r="D240" s="9">
+        <v>0</v>
+      </c>
+      <c r="E240" s="9">
+        <v>1</v>
+      </c>
+      <c r="F240" s="9">
+        <v>1</v>
+      </c>
+      <c r="G240" s="9">
+        <v>11</v>
+      </c>
+      <c r="H240" s="9">
+        <v>0</v>
+      </c>
+      <c r="I240" s="14">
+        <v>9500</v>
+      </c>
+      <c r="J240" s="9">
+        <v>1</v>
+      </c>
+      <c r="K240" s="9">
+        <v>8</v>
+      </c>
+      <c r="L240" s="9">
+        <v>350</v>
+      </c>
+      <c r="M240" s="15">
+        <v>2</v>
+      </c>
+      <c r="N240" s="9">
+        <v>7</v>
+      </c>
+      <c r="O240" s="9">
+        <v>7</v>
+      </c>
+      <c r="P240" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q240" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="R240" s="9">
+        <v>99</v>
+      </c>
+      <c r="S240" s="9">
+        <v>0</v>
+      </c>
+      <c r="W240" s="16"/>
+      <c r="Y240"/>
+      <c r="Z240"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z238" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="13" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A22 A25:A151 A153:A181 A183:A204 A220:A230 A235:A237 A239:A1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+  <autoFilter ref="A4:Z240" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A22 A25:A151 A153:A181 A183:A204 A220:A230 A235:A237 A241:A1048576">
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A22 A25:A41 A43:A44 A46:A47 A51:A52 A60:A151 A154:A179 A181 A183:A204">
-    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:A7">
-    <cfRule type="duplicateValues" dxfId="32" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A22 A25:A32 A37">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A24">
-    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36 A38:A41 A43:A44 A46:A47 A51:A52">
-    <cfRule type="duplicateValues" dxfId="27" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42">
-    <cfRule type="duplicateValues" dxfId="26" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="25" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="24" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:A59">
-    <cfRule type="duplicateValues" dxfId="20" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A152">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A153">
-    <cfRule type="duplicateValues" dxfId="17" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A180">
-    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A182">
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A205">
-    <cfRule type="duplicateValues" dxfId="14" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A220">
-    <cfRule type="duplicateValues" dxfId="13" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A221">
-    <cfRule type="duplicateValues" dxfId="12" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A231:A232">
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A233">
-    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A234">
-    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A238">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A239">
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A240">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -19102,7 +19180,7 @@
         <v>90</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>90</v>
@@ -19157,7 +19235,7 @@
         <v>90</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>90</v>
@@ -19212,7 +19290,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>90</v>
@@ -19239,7 +19317,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B4" t="s">
         <v>94</v>
@@ -19295,10 +19373,10 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
@@ -19381,7 +19459,7 @@
         <v>90</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>90</v>
@@ -19438,7 +19516,7 @@
         <v>90</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>90</v>
@@ -19486,7 +19564,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>91</v>
@@ -19495,7 +19573,7 @@
         <v>90</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>90</v>
@@ -19552,7 +19630,7 @@
         <v>90</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>90</v>
@@ -19609,7 +19687,7 @@
         <v>90</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>90</v>
@@ -19651,7 +19729,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>90</v>
@@ -19666,7 +19744,7 @@
         <v>90</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>90</v>
@@ -19723,7 +19801,7 @@
         <v>90</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>90</v>
@@ -19780,7 +19858,7 @@
         <v>90</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>90</v>
@@ -19837,7 +19915,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>90</v>
@@ -19894,7 +19972,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>90</v>
@@ -19951,7 +20029,7 @@
         <v>90</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>90</v>
@@ -20008,7 +20086,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>90</v>
@@ -20050,7 +20128,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>91</v>
@@ -20065,7 +20143,7 @@
         <v>332</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L18" s="4">
         <v>2</v>
@@ -20164,7 +20242,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>268</v>
@@ -20179,7 +20257,7 @@
         <v>90</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>90</v>
@@ -20221,7 +20299,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>268</v>
@@ -20236,7 +20314,7 @@
         <v>90</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>90</v>
@@ -20278,7 +20356,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>268</v>
@@ -20293,7 +20371,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>90</v>
@@ -20397,7 +20475,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L24" s="4">
         <v>1</v>
@@ -20454,7 +20532,7 @@
         <v>90</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>90</v>
@@ -20511,7 +20589,7 @@
         <v>332</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L26" s="4">
         <v>2</v>
@@ -20566,7 +20644,7 @@
         <v>332</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L27" s="4">
         <v>2</v>
@@ -20621,7 +20699,7 @@
         <v>332</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L28" s="4">
         <v>2</v>
@@ -20676,7 +20754,7 @@
         <v>332</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L29" s="4">
         <v>2</v>
@@ -20731,7 +20809,7 @@
         <v>332</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L30" s="4">
         <v>2</v>
@@ -20786,7 +20864,7 @@
         <v>332</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L31" s="4">
         <v>2</v>
@@ -20841,7 +20919,7 @@
         <v>332</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L32" s="4">
         <v>2</v>
@@ -20866,10 +20944,10 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C33" t="s">
         <v>89</v>
@@ -20919,7 +20997,7 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B34" t="s">
         <v>134</v>
@@ -20967,7 +21045,7 @@
         <v>110</v>
       </c>
       <c r="Q34" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R34" t="s">
         <v>89</v>
@@ -21005,7 +21083,7 @@
         <v>90</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L35" s="4">
         <v>1</v>
@@ -21062,7 +21140,7 @@
         <v>251</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L36" s="4">
         <v>2</v>
@@ -21102,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>90</v>
@@ -21117,7 +21195,7 @@
         <v>90</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L37" s="4">
         <v>1</v>
@@ -21159,7 +21237,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>90</v>
@@ -21174,7 +21252,7 @@
         <v>90</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L38" s="4" t="s">
         <v>90</v>
@@ -21231,7 +21309,7 @@
         <v>90</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>90</v>
@@ -21273,7 +21351,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>268</v>
@@ -21288,7 +21366,7 @@
         <v>90</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L40" s="4">
         <v>2</v>
@@ -21330,7 +21408,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>268</v>
@@ -21345,7 +21423,7 @@
         <v>90</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L41" s="4">
         <v>2</v>
@@ -21387,7 +21465,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>268</v>
@@ -21402,7 +21480,7 @@
         <v>90</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L42" s="4">
         <v>1</v>
@@ -21450,7 +21528,7 @@
         <v>268</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>90</v>
@@ -21459,7 +21537,7 @@
         <v>90</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>90</v>
@@ -21516,7 +21594,7 @@
         <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L44" s="4" t="s">
         <v>90</v>
@@ -21573,7 +21651,7 @@
         <v>251</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L45" s="4">
         <v>2</v>
@@ -21628,7 +21706,7 @@
         <v>251</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L46" s="4">
         <v>1</v>
@@ -21685,7 +21763,7 @@
         <v>251</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L47" s="4">
         <v>2</v>
@@ -21740,7 +21818,7 @@
         <v>90</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>90</v>
@@ -21767,7 +21845,7 @@
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
@@ -21826,7 +21904,7 @@
         <v>2040013</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
@@ -21851,7 +21929,7 @@
         <v>90</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L50" s="4" t="s">
         <v>90</v>
@@ -21879,7 +21957,7 @@
         <v>2040023</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C51" s="1">
         <v>0</v>
@@ -21904,7 +21982,7 @@
         <v>90</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L51" s="4" t="s">
         <v>90</v>
@@ -21929,10 +22007,10 @@
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D52" t="s">
         <v>89</v>
@@ -21982,10 +22060,10 @@
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D53" t="s">
         <v>89</v>
@@ -22088,7 +22166,7 @@
         <v>2040011</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" t="s">
         <v>89</v>
@@ -22141,7 +22219,7 @@
         <v>2040012</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="1">
         <v>0</v>
@@ -22166,7 +22244,7 @@
         <v>90</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L56" s="4" t="s">
         <v>90</v>
@@ -22247,7 +22325,7 @@
         <v>2040022</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -22272,7 +22350,7 @@
         <v>90</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>90</v>
@@ -22300,7 +22378,7 @@
         <v>1400001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
@@ -22325,7 +22403,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>90</v>
@@ -22408,7 +22486,7 @@
     </row>
     <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s">
         <v>184</v>
@@ -22464,7 +22542,7 @@
     </row>
     <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s">
         <v>185</v>
@@ -22520,7 +22598,7 @@
     </row>
     <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s">
         <v>186</v>
@@ -22576,7 +22654,7 @@
     </row>
     <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s">
         <v>187</v>
@@ -22632,7 +22710,7 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s">
         <v>188</v>
@@ -23755,7 +23833,7 @@
         <v>229</v>
       </c>
       <c r="B85" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C85" t="s">
         <v>89</v>
@@ -23867,7 +23945,7 @@
         <v>233</v>
       </c>
       <c r="B87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C87" t="s">
         <v>89</v>
@@ -23923,7 +24001,7 @@
         <v>235</v>
       </c>
       <c r="B88" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C88" t="s">
         <v>89</v>
@@ -24704,7 +24782,7 @@
         <v>264</v>
       </c>
       <c r="B102" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C102" t="s">
         <v>89</v>
@@ -25600,7 +25678,7 @@
         <v>298</v>
       </c>
       <c r="B118" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C118" t="s">
         <v>89</v>
@@ -25656,7 +25734,7 @@
         <v>300</v>
       </c>
       <c r="B119" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C119" t="s">
         <v>89</v>
@@ -25712,7 +25790,7 @@
         <v>302</v>
       </c>
       <c r="B120" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C120" t="s">
         <v>89</v>
@@ -25768,7 +25846,7 @@
         <v>304</v>
       </c>
       <c r="B121" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C121" t="s">
         <v>89</v>
@@ -26531,10 +26609,10 @@
     </row>
     <row r="135" spans="1:18" ht="15" customHeight="1">
       <c r="A135" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C135" t="s">
         <v>89</v>
@@ -26818,12 +26896,12 @@
         <v>90</v>
       </c>
       <c r="Q146" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="147" spans="1:18">
       <c r="A147" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B147" t="s">
         <v>336</v>
@@ -26879,7 +26957,7 @@
     </row>
     <row r="148" spans="1:18">
       <c r="A148" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B148" t="s">
         <v>337</v>
@@ -26927,7 +27005,7 @@
         <v>90</v>
       </c>
       <c r="Q148" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R148" t="s">
         <v>89</v>
@@ -26935,7 +27013,7 @@
     </row>
     <row r="149" spans="1:18">
       <c r="A149" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B149" t="s">
         <v>338</v>
@@ -26950,7 +27028,7 @@
         <v>90</v>
       </c>
       <c r="F149" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G149" t="s">
         <v>90</v>
@@ -26991,7 +27069,7 @@
     </row>
     <row r="150" spans="1:18">
       <c r="A150" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s">
         <v>339</v>
@@ -27006,7 +27084,7 @@
         <v>90</v>
       </c>
       <c r="F150" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G150" t="s">
         <v>268</v>
@@ -27039,7 +27117,7 @@
         <v>90</v>
       </c>
       <c r="Q150" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="R150" t="s">
         <v>89</v>
@@ -27103,7 +27181,7 @@
     </row>
     <row r="152" spans="1:18">
       <c r="A152" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B152" t="s">
         <v>343</v>
@@ -27159,22 +27237,22 @@
     </row>
     <row r="153" spans="1:18">
       <c r="A153" t="s">
+        <v>444</v>
+      </c>
+      <c r="B153" t="s">
         <v>344</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
+        <v>91</v>
+      </c>
+      <c r="D153" t="s">
+        <v>89</v>
+      </c>
+      <c r="E153" t="s">
+        <v>90</v>
+      </c>
+      <c r="F153" t="s">
         <v>345</v>
-      </c>
-      <c r="C153" t="s">
-        <v>91</v>
-      </c>
-      <c r="D153" t="s">
-        <v>89</v>
-      </c>
-      <c r="E153" t="s">
-        <v>90</v>
-      </c>
-      <c r="F153" t="s">
-        <v>346</v>
       </c>
       <c r="G153" t="s">
         <v>91</v>
@@ -27215,10 +27293,10 @@
     </row>
     <row r="154" spans="1:18">
       <c r="A154" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B154" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C154" t="s">
         <v>91</v>
@@ -27230,7 +27308,7 @@
         <v>0</v>
       </c>
       <c r="F154" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G154" t="s">
         <v>268</v>
@@ -27263,18 +27341,18 @@
         <v>90</v>
       </c>
       <c r="Q154" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155" spans="1:18">
       <c r="A155" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B155" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C155" t="s">
         <v>268</v>
@@ -27327,10 +27405,10 @@
     </row>
     <row r="156" spans="1:18" s="2" customFormat="1">
       <c r="A156" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
@@ -27383,10 +27461,10 @@
     </row>
     <row r="157" spans="1:18" s="2" customFormat="1">
       <c r="A157" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
@@ -27439,10 +27517,10 @@
     </row>
     <row r="158" spans="1:18" s="2" customFormat="1">
       <c r="A158" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C158" s="2">
         <v>0</v>
@@ -27492,10 +27570,10 @@
     </row>
     <row r="159" spans="1:18" s="2" customFormat="1">
       <c r="A159" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
@@ -27545,10 +27623,10 @@
     </row>
     <row r="160" spans="1:18" s="2" customFormat="1">
       <c r="A160" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C160" s="2">
         <v>0</v>
@@ -27598,7 +27676,7 @@
     </row>
     <row r="161" spans="1:18">
       <c r="A161" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B161" t="s">
         <v>148</v>
@@ -27702,15 +27780,15 @@
         <v>268</v>
       </c>
       <c r="Q162" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="R162" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="163" spans="1:18">
       <c r="A163" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B163" t="s">
         <v>151</v>
@@ -27758,7 +27836,7 @@
         <v>268</v>
       </c>
       <c r="Q163" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="R163" t="s">
         <v>89</v>
@@ -27766,7 +27844,7 @@
     </row>
     <row r="164" spans="1:18">
       <c r="A164" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B164" t="s">
         <v>150</v>
@@ -27814,18 +27892,18 @@
         <v>268</v>
       </c>
       <c r="Q164" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R164" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="165" spans="1:18">
       <c r="A165" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B165" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C165" t="s">
         <v>91</v>
@@ -27878,10 +27956,10 @@
     </row>
     <row r="166" spans="1:18">
       <c r="A166" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C166" t="s">
         <v>91</v>
@@ -27926,18 +28004,18 @@
         <v>268</v>
       </c>
       <c r="Q166" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="R166" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="167" spans="1:18">
       <c r="A167" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B167" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C167" t="s">
         <v>91</v>
@@ -27985,15 +28063,15 @@
         <v>271</v>
       </c>
       <c r="R167" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="168" spans="1:18">
       <c r="A168" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B168" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C168" t="s">
         <v>91</v>
@@ -28005,7 +28083,7 @@
         <v>90</v>
       </c>
       <c r="F168" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G168" t="s">
         <v>90</v>
@@ -28046,10 +28124,10 @@
     </row>
     <row r="169" spans="1:18">
       <c r="A169" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B169" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C169" t="s">
         <v>91</v>
@@ -28094,7 +28172,7 @@
         <v>268</v>
       </c>
       <c r="Q169" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R169" t="s">
         <v>89</v>
@@ -28102,10 +28180,10 @@
     </row>
     <row r="170" spans="1:18">
       <c r="A170" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B170" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C170" t="s">
         <v>91</v>
@@ -28117,7 +28195,7 @@
         <v>90</v>
       </c>
       <c r="F170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G170" t="s">
         <v>268</v>
@@ -28150,18 +28228,18 @@
         <v>268</v>
       </c>
       <c r="Q170" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R170" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="171" spans="1:18">
       <c r="A171" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B171" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C171" t="s">
         <v>91</v>
@@ -28214,10 +28292,10 @@
     </row>
     <row r="172" spans="1:18">
       <c r="A172" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B172" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C172" t="s">
         <v>91</v>
@@ -28270,10 +28348,10 @@
     </row>
     <row r="173" spans="1:18">
       <c r="A173" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B173" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C173" t="s">
         <v>91</v>
@@ -28285,7 +28363,7 @@
         <v>90</v>
       </c>
       <c r="F173" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G173" t="s">
         <v>268</v>
@@ -28318,7 +28396,7 @@
         <v>268</v>
       </c>
       <c r="Q173" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R173" t="s">
         <v>89</v>
@@ -28326,10 +28404,10 @@
     </row>
     <row r="174" spans="1:18">
       <c r="A174" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B174" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C174" t="s">
         <v>91</v>
@@ -28341,7 +28419,7 @@
         <v>90</v>
       </c>
       <c r="F174" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G174" t="s">
         <v>268</v>
@@ -28374,7 +28452,7 @@
         <v>268</v>
       </c>
       <c r="Q174" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="R174" t="s">
         <v>89</v>
@@ -28382,10 +28460,10 @@
     </row>
     <row r="175" spans="1:18">
       <c r="A175" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B175" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C175" t="s">
         <v>91</v>
@@ -28397,7 +28475,7 @@
         <v>90</v>
       </c>
       <c r="F175" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G175" t="s">
         <v>268</v>
@@ -28430,7 +28508,7 @@
         <v>268</v>
       </c>
       <c r="Q175" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R175" t="s">
         <v>89</v>
@@ -28438,10 +28516,10 @@
     </row>
     <row r="176" spans="1:18">
       <c r="A176" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B176" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C176" t="s">
         <v>91</v>
@@ -28453,7 +28531,7 @@
         <v>90</v>
       </c>
       <c r="F176" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G176" t="s">
         <v>268</v>
@@ -28486,7 +28564,7 @@
         <v>268</v>
       </c>
       <c r="Q176" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="R176" t="s">
         <v>89</v>
@@ -28494,10 +28572,10 @@
     </row>
     <row r="177" spans="1:18">
       <c r="A177" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B177" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C177" t="s">
         <v>91</v>
@@ -28509,7 +28587,7 @@
         <v>90</v>
       </c>
       <c r="F177" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G177" t="s">
         <v>90</v>
@@ -28542,14 +28620,14 @@
         <v>268</v>
       </c>
       <c r="Q177" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="R177" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
@@ -28583,7 +28661,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData/>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_skill.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_skill" sheetId="1" r:id="rId1"/>
@@ -12,7 +17,7 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill!$A$4:$Z$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_skill!$A$4:$Z$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="483">
   <si>
     <t>技能id</t>
   </si>
@@ -2978,7 +2983,7 @@
     <t>火龙王攻击技能（额外5%最大生命值伤害）</t>
   </si>
   <si>
-    <t>突袭（大师技）</t>
+    <t>强袭（大师技）</t>
   </si>
   <si>
     <t>血腥风暴（大师技）</t>
@@ -3273,6 +3278,9 @@
     <t>惩戒屏障</t>
   </si>
   <si>
+    <t>强袭啊</t>
+  </si>
+  <si>
     <t>700</t>
   </si>
   <si>
@@ -3431,6 +3439,9 @@
   </si>
   <si>
     <t>玛雅之手2格群体普攻</t>
+  </si>
+  <si>
+    <t>突袭（大师技）</t>
   </si>
   <si>
     <t>1012020</t>
@@ -4954,7 +4965,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z240"/>
+  <dimension ref="A1:Z241"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.2857142857143" style="2" customWidth="1"/>
@@ -14523,35 +14534,38 @@
       <c r="T153"/>
       <c r="W153" s="19"/>
     </row>
-    <row r="154" s="2" customFormat="1" spans="1:26">
+    <row r="154" s="12" customFormat="1" spans="1:26">
       <c r="A154" s="2">
         <v>1040001</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C154" s="2">
-        <v>0</v>
-      </c>
-      <c r="D154" s="2">
-        <v>0</v>
-      </c>
-      <c r="E154" s="2">
-        <v>2</v>
-      </c>
-      <c r="G154" s="2">
-        <v>20</v>
-      </c>
-      <c r="H154" s="2">
+      <c r="C154" s="12">
+        <v>0</v>
+      </c>
+      <c r="D154" s="12">
+        <v>0</v>
+      </c>
+      <c r="E154" s="12">
+        <v>1</v>
+      </c>
+      <c r="F154" s="12">
+        <v>1</v>
+      </c>
+      <c r="G154" s="12">
+        <v>5</v>
+      </c>
+      <c r="H154" s="12">
         <v>1</v>
       </c>
       <c r="I154" s="17">
         <v>10000</v>
       </c>
-      <c r="J154" s="2">
-        <v>0</v>
-      </c>
-      <c r="K154" s="2">
+      <c r="J154" s="12">
+        <v>1</v>
+      </c>
+      <c r="K154" s="12">
         <v>1</v>
       </c>
       <c r="L154" s="12">
@@ -14560,28 +14574,32 @@
       <c r="M154" s="18">
         <v>1</v>
       </c>
-      <c r="N154" s="2">
-        <v>1</v>
-      </c>
-      <c r="O154" s="2">
-        <v>1</v>
-      </c>
-      <c r="P154" s="2">
-        <v>0</v>
+      <c r="N154" s="12">
+        <v>7</v>
+      </c>
+      <c r="O154" s="12">
+        <v>7</v>
+      </c>
+      <c r="P154" s="12">
+        <v>1</v>
       </c>
       <c r="Q154" s="2">
-        <v>1</v>
-      </c>
-      <c r="R154" s="2">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="R154" s="12">
+        <v>11</v>
       </c>
       <c r="S154" s="12">
         <v>0</v>
       </c>
-      <c r="T154" s="12"/>
-      <c r="W154" s="19"/>
-      <c r="Y154"/>
-      <c r="Z154"/>
+      <c r="T154" s="12">
+        <v>1</v>
+      </c>
+      <c r="W154" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y154" s="1"/>
+      <c r="Z154" s="1"/>
     </row>
     <row r="155" s="2" customFormat="1" spans="1:26">
       <c r="A155" s="2">
@@ -14618,7 +14636,7 @@
         <v>350</v>
       </c>
       <c r="M155" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N155" s="2">
         <v>7</v>
@@ -14627,7 +14645,7 @@
         <v>7</v>
       </c>
       <c r="P155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q155" s="2">
         <v>2</v>
@@ -17191,10 +17209,10 @@
         <v>7</v>
       </c>
       <c r="O198" s="13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P198" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q198" s="13">
         <v>2</v>
@@ -17807,10 +17825,10 @@
         <v>7</v>
       </c>
       <c r="P208" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q208" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R208" s="14">
         <v>11</v>
@@ -18181,16 +18199,16 @@
         <v>1</v>
       </c>
       <c r="N214" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O214" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P214" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q214" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R214" s="14">
         <v>6</v>
@@ -19772,93 +19790,169 @@
       <c r="Y240"/>
       <c r="Z240"/>
     </row>
+    <row r="241" s="12" customFormat="1" spans="1:26">
+      <c r="A241" s="12">
+        <v>1011001</v>
+      </c>
+      <c r="B241" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="C241" s="12">
+        <v>0</v>
+      </c>
+      <c r="D241" s="12">
+        <v>0</v>
+      </c>
+      <c r="E241" s="12">
+        <v>1</v>
+      </c>
+      <c r="F241" s="12">
+        <v>1</v>
+      </c>
+      <c r="G241" s="12">
+        <v>5</v>
+      </c>
+      <c r="H241" s="12">
+        <v>1</v>
+      </c>
+      <c r="I241" s="17">
+        <v>10000</v>
+      </c>
+      <c r="J241" s="12">
+        <v>1</v>
+      </c>
+      <c r="K241" s="12">
+        <v>1</v>
+      </c>
+      <c r="L241" s="12">
+        <v>350</v>
+      </c>
+      <c r="M241" s="18">
+        <v>1</v>
+      </c>
+      <c r="N241" s="12">
+        <v>7</v>
+      </c>
+      <c r="O241" s="12">
+        <v>5</v>
+      </c>
+      <c r="P241" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q241" s="2">
+        <v>2</v>
+      </c>
+      <c r="R241" s="12">
+        <v>11</v>
+      </c>
+      <c r="S241" s="12">
+        <v>1</v>
+      </c>
+      <c r="T241" s="12">
+        <v>1</v>
+      </c>
+      <c r="W241" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y241" s="1"/>
+      <c r="Z241" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:Z240" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:Z241" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
     <cfRule type="duplicateValues" dxfId="0" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A42">
+  <conditionalFormatting sqref="A49">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A152">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A153">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A154">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A180">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A182">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A205">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A220">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A221">
     <cfRule type="duplicateValues" dxfId="0" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  <conditionalFormatting sqref="A233">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  <conditionalFormatting sqref="A234">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
+  <conditionalFormatting sqref="A238">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A239">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A240">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A241">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:A7">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A24">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:A59">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A231:A232">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A22 A25:A151 A153 A155:A181 A183:A204 A220:A230 A235:A237 A242:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A152">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A153">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A180">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A182">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A205">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A220">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A221">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A233">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A234">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A238">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A239">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A240">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A7">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A24">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54:A59">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A231:A232">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A22 A25:A151 A153:A181 A183:A204 A220:A230 A235:A237 A241:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A22 A25:A41 A43:A44 A46:A47 A51:A52 A60:A151 A154:A179 A181 A183:A204">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  <conditionalFormatting sqref="A5:A22 A25:A41 A43:A44 A46:A47 A51:A52 A60:A151 A155:A179 A181 A183:A204">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A22 A25:A32 A37">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36 A38:A41 A43:A44 A46:A47 A51:A52">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -19907,7 +20001,7 @@
         <v>90</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>90</v>
@@ -19962,7 +20056,7 @@
         <v>90</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>90</v>
@@ -20017,7 +20111,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>90</v>
@@ -20044,7 +20138,7 @@
     </row>
     <row r="4" customFormat="1" spans="1:19">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B4" t="s">
         <v>94</v>
@@ -20100,7 +20194,7 @@
     </row>
     <row r="5" customFormat="1" spans="1:19">
       <c r="A5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B5" t="s">
         <v>360</v>
@@ -20186,7 +20280,7 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>90</v>
@@ -20243,7 +20337,7 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>90</v>
@@ -20291,7 +20385,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>91</v>
@@ -20300,7 +20394,7 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>90</v>
@@ -20357,7 +20451,7 @@
         <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>90</v>
@@ -20414,7 +20508,7 @@
         <v>90</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>90</v>
@@ -20456,7 +20550,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>90</v>
@@ -20471,7 +20565,7 @@
         <v>90</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>90</v>
@@ -20528,7 +20622,7 @@
         <v>90</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>90</v>
@@ -20585,7 +20679,7 @@
         <v>90</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>90</v>
@@ -20642,7 +20736,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>90</v>
@@ -20699,7 +20793,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>90</v>
@@ -20756,7 +20850,7 @@
         <v>90</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>90</v>
@@ -20813,7 +20907,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>90</v>
@@ -20855,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>91</v>
@@ -20870,7 +20964,7 @@
         <v>332</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L18" s="5">
         <v>2</v>
@@ -20984,7 +21078,7 @@
         <v>90</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>90</v>
@@ -21026,7 +21120,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>268</v>
@@ -21041,7 +21135,7 @@
         <v>90</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>90</v>
@@ -21083,7 +21177,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>268</v>
@@ -21098,7 +21192,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>90</v>
@@ -21203,7 +21297,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L24" s="5">
         <v>1</v>
@@ -21260,7 +21354,7 @@
         <v>90</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>90</v>
@@ -21317,7 +21411,7 @@
         <v>332</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L26" s="5">
         <v>2</v>
@@ -21372,7 +21466,7 @@
         <v>332</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -21427,7 +21521,7 @@
         <v>332</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L28" s="5">
         <v>2</v>
@@ -21482,7 +21576,7 @@
         <v>332</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L29" s="5">
         <v>2</v>
@@ -21537,7 +21631,7 @@
         <v>332</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L30" s="5">
         <v>2</v>
@@ -21592,7 +21686,7 @@
         <v>332</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L31" s="5">
         <v>2</v>
@@ -21647,7 +21741,7 @@
         <v>332</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L32" s="5">
         <v>2</v>
@@ -21672,10 +21766,10 @@
     </row>
     <row r="33" customFormat="1" spans="1:19">
       <c r="A33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>89</v>
@@ -21725,7 +21819,7 @@
     </row>
     <row r="34" customFormat="1" spans="1:19">
       <c r="A34" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B34" t="s">
         <v>134</v>
@@ -21773,7 +21867,7 @@
         <v>110</v>
       </c>
       <c r="Q34" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R34" t="s">
         <v>89</v>
@@ -21811,7 +21905,7 @@
         <v>90</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L35" s="5">
         <v>1</v>
@@ -21868,7 +21962,7 @@
         <v>251</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L36" s="5">
         <v>2</v>
@@ -21908,7 +22002,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>90</v>
@@ -21923,7 +22017,7 @@
         <v>90</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L37" s="5">
         <v>1</v>
@@ -21965,7 +22059,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>90</v>
@@ -21980,7 +22074,7 @@
         <v>90</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>90</v>
@@ -22037,7 +22131,7 @@
         <v>90</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>90</v>
@@ -22079,7 +22173,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>268</v>
@@ -22094,7 +22188,7 @@
         <v>90</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L40" s="5">
         <v>2</v>
@@ -22136,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>268</v>
@@ -22151,7 +22245,7 @@
         <v>90</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L41" s="5">
         <v>2</v>
@@ -22193,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>268</v>
@@ -22208,7 +22302,7 @@
         <v>90</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L42" s="5">
         <v>1</v>
@@ -22256,7 +22350,7 @@
         <v>268</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>90</v>
@@ -22265,7 +22359,7 @@
         <v>90</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>90</v>
@@ -22322,7 +22416,7 @@
         <v>90</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>90</v>
@@ -22379,7 +22473,7 @@
         <v>251</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L45" s="5">
         <v>2</v>
@@ -22434,7 +22528,7 @@
         <v>251</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L46" s="5">
         <v>1</v>
@@ -22491,7 +22585,7 @@
         <v>251</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L47" s="5">
         <v>2</v>
@@ -22546,7 +22640,7 @@
         <v>90</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>90</v>
@@ -22573,7 +22667,7 @@
     </row>
     <row r="49" customFormat="1" spans="1:19">
       <c r="A49" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
@@ -22632,7 +22726,7 @@
         <v>2040013</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C50" s="4">
         <v>0</v>
@@ -22657,7 +22751,7 @@
         <v>90</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>90</v>
@@ -22685,7 +22779,7 @@
         <v>2040023</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C51" s="4">
         <v>0</v>
@@ -22710,7 +22804,7 @@
         <v>90</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>90</v>
@@ -22735,10 +22829,10 @@
     </row>
     <row r="52" customFormat="1" spans="1:19">
       <c r="A52" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" t="s">
@@ -22789,10 +22883,10 @@
     </row>
     <row r="53" customFormat="1" spans="1:19">
       <c r="A53" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" t="s">
@@ -22896,7 +22990,7 @@
         <v>2040011</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>89</v>
@@ -22949,7 +23043,7 @@
         <v>2040012</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="4">
         <v>0</v>
@@ -22974,7 +23068,7 @@
         <v>90</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>90</v>
@@ -23055,7 +23149,7 @@
         <v>2040022</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="4">
         <v>0</v>
@@ -23080,7 +23174,7 @@
         <v>90</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>90</v>
@@ -23133,7 +23227,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>90</v>
@@ -23216,7 +23310,7 @@
     </row>
     <row r="61" customFormat="1" spans="1:19">
       <c r="A61" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s">
         <v>184</v>
@@ -23272,7 +23366,7 @@
     </row>
     <row r="62" customFormat="1" spans="1:19">
       <c r="A62" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s">
         <v>185</v>
@@ -23328,7 +23422,7 @@
     </row>
     <row r="63" customFormat="1" spans="1:19">
       <c r="A63" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s">
         <v>186</v>
@@ -23384,7 +23478,7 @@
     </row>
     <row r="64" customFormat="1" spans="1:19">
       <c r="A64" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s">
         <v>187</v>
@@ -23440,7 +23534,7 @@
     </row>
     <row r="65" customFormat="1" spans="1:18">
       <c r="A65" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s">
         <v>188</v>
@@ -24563,7 +24657,7 @@
         <v>229</v>
       </c>
       <c r="B85" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>89</v>
@@ -24675,7 +24769,7 @@
         <v>233</v>
       </c>
       <c r="B87" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>89</v>
@@ -24731,7 +24825,7 @@
         <v>235</v>
       </c>
       <c r="B88" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>89</v>
@@ -25513,7 +25607,7 @@
         <v>264</v>
       </c>
       <c r="B102" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>89</v>
@@ -26409,7 +26503,7 @@
         <v>298</v>
       </c>
       <c r="B118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>89</v>
@@ -26465,7 +26559,7 @@
         <v>300</v>
       </c>
       <c r="B119" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>89</v>
@@ -26521,7 +26615,7 @@
         <v>302</v>
       </c>
       <c r="B120" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>89</v>
@@ -26577,7 +26671,7 @@
         <v>304</v>
       </c>
       <c r="B121" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>89</v>
@@ -26633,7 +26727,7 @@
         <v>1040001</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>308</v>
+        <v>435</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -27340,10 +27434,10 @@
     </row>
     <row r="135" customFormat="1" customHeight="1" spans="1:18">
       <c r="A135" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>89</v>
@@ -27634,12 +27728,12 @@
         <v>90</v>
       </c>
       <c r="Q146" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="147" customFormat="1" spans="1:18">
       <c r="A147" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B147" t="s">
         <v>336</v>
@@ -27695,7 +27789,7 @@
     </row>
     <row r="148" customFormat="1" spans="1:18">
       <c r="A148" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B148" t="s">
         <v>337</v>
@@ -27743,7 +27837,7 @@
         <v>90</v>
       </c>
       <c r="Q148" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R148" t="s">
         <v>89</v>
@@ -27751,7 +27845,7 @@
     </row>
     <row r="149" customFormat="1" spans="1:18">
       <c r="A149" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B149" t="s">
         <v>338</v>
@@ -27766,7 +27860,7 @@
         <v>90</v>
       </c>
       <c r="F149" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G149" t="s">
         <v>90</v>
@@ -27807,7 +27901,7 @@
     </row>
     <row r="150" customFormat="1" spans="1:18">
       <c r="A150" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B150" t="s">
         <v>339</v>
@@ -27822,7 +27916,7 @@
         <v>90</v>
       </c>
       <c r="F150" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G150" t="s">
         <v>268</v>
@@ -27855,7 +27949,7 @@
         <v>90</v>
       </c>
       <c r="Q150" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="R150" t="s">
         <v>89</v>
@@ -27919,7 +28013,7 @@
     </row>
     <row r="152" customFormat="1" spans="1:18">
       <c r="A152" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B152" t="s">
         <v>343</v>
@@ -27975,7 +28069,7 @@
     </row>
     <row r="153" customFormat="1" spans="1:18">
       <c r="A153" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B153" t="s">
         <v>344</v>
@@ -28031,10 +28125,10 @@
     </row>
     <row r="154" customFormat="1" spans="1:18">
       <c r="A154" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B154" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>91</v>
@@ -28079,15 +28173,15 @@
         <v>90</v>
       </c>
       <c r="Q154" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="R154" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="155" customFormat="1" spans="1:18">
       <c r="A155" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B155" t="s">
         <v>346</v>
@@ -28143,7 +28237,7 @@
     </row>
     <row r="156" s="2" customFormat="1" spans="1:18">
       <c r="A156" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>347</v>
@@ -28199,7 +28293,7 @@
     </row>
     <row r="157" s="2" customFormat="1" spans="1:18">
       <c r="A157" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B157" s="8" t="s">
         <v>348</v>
@@ -28255,7 +28349,7 @@
     </row>
     <row r="158" s="2" customFormat="1" spans="1:18">
       <c r="A158" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>349</v>
@@ -28308,7 +28402,7 @@
     </row>
     <row r="159" s="2" customFormat="1" spans="1:18">
       <c r="A159" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>350</v>
@@ -28361,7 +28455,7 @@
     </row>
     <row r="160" s="2" customFormat="1" spans="1:18">
       <c r="A160" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>351</v>
@@ -28414,7 +28508,7 @@
     </row>
     <row r="161" customFormat="1" spans="1:18">
       <c r="A161" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B161" t="s">
         <v>148</v>
@@ -28518,15 +28612,15 @@
         <v>268</v>
       </c>
       <c r="Q162" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="R162" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:18">
       <c r="A163" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B163" t="s">
         <v>151</v>
@@ -28574,7 +28668,7 @@
         <v>268</v>
       </c>
       <c r="Q163" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R163" t="s">
         <v>89</v>
@@ -28582,7 +28676,7 @@
     </row>
     <row r="164" customFormat="1" spans="1:18">
       <c r="A164" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B164" t="s">
         <v>150</v>
@@ -28630,18 +28724,18 @@
         <v>268</v>
       </c>
       <c r="Q164" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="R164" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="165" customFormat="1" spans="1:18">
       <c r="A165" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B165" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>91</v>
@@ -28694,7 +28788,7 @@
     </row>
     <row r="166" customFormat="1" spans="1:18">
       <c r="A166" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B166" t="s">
         <v>377</v>
@@ -28742,15 +28836,15 @@
         <v>268</v>
       </c>
       <c r="Q166" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R166" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:18">
       <c r="A167" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B167" t="s">
         <v>378</v>
@@ -28801,12 +28895,12 @@
         <v>271</v>
       </c>
       <c r="R167" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:18">
       <c r="A168" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B168" t="s">
         <v>352</v>
@@ -28821,7 +28915,7 @@
         <v>90</v>
       </c>
       <c r="F168" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G168" t="s">
         <v>90</v>
@@ -28862,7 +28956,7 @@
     </row>
     <row r="169" customFormat="1" spans="1:18">
       <c r="A169" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B169" t="s">
         <v>375</v>
@@ -28910,7 +29004,7 @@
         <v>268</v>
       </c>
       <c r="Q169" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="R169" t="s">
         <v>89</v>
@@ -28918,7 +29012,7 @@
     </row>
     <row r="170" customFormat="1" spans="1:18">
       <c r="A170" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B170" t="s">
         <v>353</v>
@@ -28933,7 +29027,7 @@
         <v>90</v>
       </c>
       <c r="F170" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G170" t="s">
         <v>268</v>
@@ -28966,15 +29060,15 @@
         <v>268</v>
       </c>
       <c r="Q170" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="R170" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:18">
       <c r="A171" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B171" t="s">
         <v>354</v>
@@ -29030,7 +29124,7 @@
     </row>
     <row r="172" customFormat="1" spans="1:18">
       <c r="A172" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B172" t="s">
         <v>355</v>
@@ -29086,7 +29180,7 @@
     </row>
     <row r="173" customFormat="1" spans="1:18">
       <c r="A173" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B173" t="s">
         <v>356</v>
@@ -29101,7 +29195,7 @@
         <v>90</v>
       </c>
       <c r="F173" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G173" t="s">
         <v>268</v>
@@ -29134,7 +29228,7 @@
         <v>268</v>
       </c>
       <c r="Q173" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="R173" t="s">
         <v>89</v>
@@ -29142,7 +29236,7 @@
     </row>
     <row r="174" customFormat="1" spans="1:18">
       <c r="A174" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B174" t="s">
         <v>357</v>
@@ -29190,7 +29284,7 @@
         <v>268</v>
       </c>
       <c r="Q174" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="R174" t="s">
         <v>89</v>
@@ -29198,7 +29292,7 @@
     </row>
     <row r="175" customFormat="1" spans="1:18">
       <c r="A175" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B175" t="s">
         <v>358</v>
@@ -29246,7 +29340,7 @@
         <v>268</v>
       </c>
       <c r="Q175" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="R175" t="s">
         <v>89</v>
@@ -29254,7 +29348,7 @@
     </row>
     <row r="176" customFormat="1" spans="1:18">
       <c r="A176" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B176" t="s">
         <v>359</v>
@@ -29302,7 +29396,7 @@
         <v>268</v>
       </c>
       <c r="Q176" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="R176" t="s">
         <v>89</v>
@@ -29310,7 +29404,7 @@
     </row>
     <row r="177" customFormat="1" spans="1:18">
       <c r="A177" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B177" t="s">
         <v>376</v>
@@ -29358,10 +29452,10 @@
         <v>268</v>
       </c>
       <c r="Q177" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="R177" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
